--- a/HR_factors.xlsx
+++ b/HR_factors.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brend\Desktop\projects\homerun\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brend\Documents\GitHub\homerun_model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00AB98E0-5CB6-4AED-9434-DD32887274CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{175D1976-E5E2-4323-ABFA-341AD6B6FCA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="15165" windowHeight="10575" xr2:uid="{5F756707-5AD7-439A-B4DC-090231B89164}"/>
+    <workbookView xWindow="12285" yWindow="2685" windowWidth="16080" windowHeight="10575" xr2:uid="{5F756707-5AD7-439A-B4DC-090231B89164}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="95">
   <si>
     <t>LAA</t>
   </si>
@@ -143,10 +143,187 @@
     <t>WSH</t>
   </si>
   <si>
-    <t>ARI</t>
-  </si>
-  <si>
     <t>team_id</t>
+  </si>
+  <si>
+    <t>Reds</t>
+  </si>
+  <si>
+    <t>Dodgers</t>
+  </si>
+  <si>
+    <t>Yankees</t>
+  </si>
+  <si>
+    <t>Rockies</t>
+  </si>
+  <si>
+    <t>White Sox</t>
+  </si>
+  <si>
+    <t>Angels</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Phillies</t>
+  </si>
+  <si>
+    <t>Brewers</t>
+  </si>
+  <si>
+    <t>Orioles</t>
+  </si>
+  <si>
+    <t>Guardians</t>
+  </si>
+  <si>
+    <t>Red Sox</t>
+  </si>
+  <si>
+    <t>Blue Jays</t>
+  </si>
+  <si>
+    <t>Twins</t>
+  </si>
+  <si>
+    <t>Nationals</t>
+  </si>
+  <si>
+    <t>Mets</t>
+  </si>
+  <si>
+    <t>Padres</t>
+  </si>
+  <si>
+    <t>Marlins</t>
+  </si>
+  <si>
+    <t>Astros</t>
+  </si>
+  <si>
+    <t>Cubs</t>
+  </si>
+  <si>
+    <t>Athletics</t>
+  </si>
+  <si>
+    <t>Mariners</t>
+  </si>
+  <si>
+    <t>Rays</t>
+  </si>
+  <si>
+    <t>Braves</t>
+  </si>
+  <si>
+    <t>Royals</t>
+  </si>
+  <si>
+    <t>Tigers</t>
+  </si>
+  <si>
+    <t>Pirates</t>
+  </si>
+  <si>
+    <t>Cardinals</t>
+  </si>
+  <si>
+    <t>Diamondbacks</t>
+  </si>
+  <si>
+    <t>Giants</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>Cincinnati</t>
+  </si>
+  <si>
+    <t>Los Angeles</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>Colorado</t>
+  </si>
+  <si>
+    <t>Chicago</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>Philadelphia</t>
+  </si>
+  <si>
+    <t>Milwaukee</t>
+  </si>
+  <si>
+    <t>Baltimore</t>
+  </si>
+  <si>
+    <t>Cleveland</t>
+  </si>
+  <si>
+    <t>Boston</t>
+  </si>
+  <si>
+    <t>Toronto</t>
+  </si>
+  <si>
+    <t>Minnesota</t>
+  </si>
+  <si>
+    <t>Washington</t>
+  </si>
+  <si>
+    <t>San Diego</t>
+  </si>
+  <si>
+    <t>Miami</t>
+  </si>
+  <si>
+    <t>Houston</t>
+  </si>
+  <si>
+    <t>Oakland</t>
+  </si>
+  <si>
+    <t>Seattle</t>
+  </si>
+  <si>
+    <t>Tampa Bay</t>
+  </si>
+  <si>
+    <t>Atlanta</t>
+  </si>
+  <si>
+    <t>Kansas City</t>
+  </si>
+  <si>
+    <t>Detroit</t>
+  </si>
+  <si>
+    <t>Pittsburgh</t>
+  </si>
+  <si>
+    <t>St. Louis</t>
+  </si>
+  <si>
+    <t>Arizona</t>
+  </si>
+  <si>
+    <t>San Francisco</t>
+  </si>
+  <si>
+    <t>team</t>
+  </si>
+  <si>
+    <t>AZ</t>
   </si>
 </sst>
 </file>
@@ -521,13 +698,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B19E0F6F-4091-44B6-8908-ADD872FB2D48}">
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>26</v>
       </c>
@@ -538,10 +717,16 @@
         <v>23</v>
       </c>
       <c r="D1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="E1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -554,8 +739,14 @@
       <c r="D2">
         <v>113</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -568,8 +759,14 @@
       <c r="D3">
         <v>113</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
@@ -582,8 +779,14 @@
       <c r="D4">
         <v>119</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -596,8 +799,14 @@
       <c r="D5">
         <v>147</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -610,8 +819,14 @@
       <c r="D6">
         <v>115</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>28</v>
       </c>
@@ -624,8 +839,14 @@
       <c r="D7">
         <v>145</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
@@ -638,8 +859,14 @@
       <c r="D8">
         <v>108</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -652,8 +879,14 @@
       <c r="D9">
         <v>140</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -666,8 +899,14 @@
       <c r="D10">
         <v>108</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -680,8 +919,14 @@
       <c r="D11">
         <v>143</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
@@ -694,8 +939,14 @@
       <c r="D12">
         <v>158</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>28</v>
       </c>
@@ -708,8 +959,14 @@
       <c r="D13">
         <v>145</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>5</v>
       </c>
@@ -722,8 +979,14 @@
       <c r="D14">
         <v>147</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>1</v>
       </c>
@@ -736,8 +999,14 @@
       <c r="D15">
         <v>110</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>2</v>
       </c>
@@ -750,8 +1019,14 @@
       <c r="D16">
         <v>114</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>13</v>
       </c>
@@ -764,8 +1039,14 @@
       <c r="D17">
         <v>115</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
@@ -778,8 +1059,14 @@
       <c r="D18">
         <v>111</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E18" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>16</v>
       </c>
@@ -792,8 +1079,14 @@
       <c r="D19">
         <v>119</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>9</v>
       </c>
@@ -806,8 +1099,14 @@
       <c r="D20">
         <v>141</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>4</v>
       </c>
@@ -820,8 +1119,14 @@
       <c r="D21">
         <v>142</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E21" t="s">
+        <v>48</v>
+      </c>
+      <c r="F21" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
@@ -834,8 +1139,14 @@
       <c r="D22">
         <v>143</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E22" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>17</v>
       </c>
@@ -848,8 +1159,14 @@
       <c r="D23">
         <v>158</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>33</v>
       </c>
@@ -862,8 +1179,14 @@
       <c r="D24">
         <v>120</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24" t="s">
+        <v>49</v>
+      </c>
+      <c r="F24" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>18</v>
       </c>
@@ -876,8 +1199,14 @@
       <c r="D25">
         <v>121</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E25" t="s">
+        <v>50</v>
+      </c>
+      <c r="F25" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
@@ -890,8 +1219,14 @@
       <c r="D26">
         <v>135</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E26" t="s">
+        <v>51</v>
+      </c>
+      <c r="F26" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>29</v>
       </c>
@@ -904,8 +1239,14 @@
       <c r="D27">
         <v>135</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E27" t="s">
+        <v>51</v>
+      </c>
+      <c r="F27" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>14</v>
       </c>
@@ -918,8 +1259,14 @@
       <c r="D28">
         <v>146</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E28" t="s">
+        <v>52</v>
+      </c>
+      <c r="F28" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>15</v>
       </c>
@@ -932,8 +1279,14 @@
       <c r="D29">
         <v>117</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E29" t="s">
+        <v>53</v>
+      </c>
+      <c r="F29" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>8</v>
       </c>
@@ -946,8 +1299,14 @@
       <c r="D30">
         <v>140</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E30" t="s">
+        <v>41</v>
+      </c>
+      <c r="F30" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>15</v>
       </c>
@@ -960,8 +1319,14 @@
       <c r="D31">
         <v>117</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E31" t="s">
+        <v>53</v>
+      </c>
+      <c r="F31" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>33</v>
       </c>
@@ -974,8 +1339,14 @@
       <c r="D32">
         <v>120</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E32" t="s">
+        <v>49</v>
+      </c>
+      <c r="F32" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>11</v>
       </c>
@@ -988,8 +1359,14 @@
       <c r="D33">
         <v>112</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E33" t="s">
+        <v>54</v>
+      </c>
+      <c r="F33" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>6</v>
       </c>
@@ -1002,8 +1379,14 @@
       <c r="D34">
         <v>133</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E34" t="s">
+        <v>55</v>
+      </c>
+      <c r="F34" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>6</v>
       </c>
@@ -1016,8 +1399,14 @@
       <c r="D35">
         <v>133</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E35" t="s">
+        <v>55</v>
+      </c>
+      <c r="F35" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>7</v>
       </c>
@@ -1030,8 +1419,14 @@
       <c r="D36">
         <v>136</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E36" t="s">
+        <v>56</v>
+      </c>
+      <c r="F36" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>30</v>
       </c>
@@ -1044,8 +1439,14 @@
       <c r="D37">
         <v>139</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E37" t="s">
+        <v>57</v>
+      </c>
+      <c r="F37" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>11</v>
       </c>
@@ -1058,8 +1459,14 @@
       <c r="D38">
         <v>112</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E38" t="s">
+        <v>54</v>
+      </c>
+      <c r="F38" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>10</v>
       </c>
@@ -1072,8 +1479,14 @@
       <c r="D39">
         <v>144</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E39" t="s">
+        <v>58</v>
+      </c>
+      <c r="F39" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>31</v>
       </c>
@@ -1086,8 +1499,14 @@
       <c r="D40">
         <v>118</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E40" t="s">
+        <v>59</v>
+      </c>
+      <c r="F40" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>18</v>
       </c>
@@ -1100,8 +1519,14 @@
       <c r="D41">
         <v>121</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E41" t="s">
+        <v>50</v>
+      </c>
+      <c r="F41" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>10</v>
       </c>
@@ -1114,8 +1539,14 @@
       <c r="D42">
         <v>144</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E42" t="s">
+        <v>58</v>
+      </c>
+      <c r="F42" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>27</v>
       </c>
@@ -1128,8 +1559,14 @@
       <c r="D43">
         <v>111</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E43" t="s">
+        <v>46</v>
+      </c>
+      <c r="F43" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>2</v>
       </c>
@@ -1142,8 +1579,14 @@
       <c r="D44">
         <v>114</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E44" t="s">
+        <v>45</v>
+      </c>
+      <c r="F44" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>4</v>
       </c>
@@ -1156,8 +1599,14 @@
       <c r="D45">
         <v>142</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E45" t="s">
+        <v>48</v>
+      </c>
+      <c r="F45" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>3</v>
       </c>
@@ -1170,8 +1619,14 @@
       <c r="D46">
         <v>116</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E46" t="s">
+        <v>60</v>
+      </c>
+      <c r="F46" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>20</v>
       </c>
@@ -1184,8 +1639,14 @@
       <c r="D47">
         <v>134</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E47" t="s">
+        <v>61</v>
+      </c>
+      <c r="F47" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>21</v>
       </c>
@@ -1198,8 +1659,14 @@
       <c r="D48">
         <v>138</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E48" t="s">
+        <v>62</v>
+      </c>
+      <c r="F48" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,8 +1679,14 @@
       <c r="D49">
         <v>146</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E49" t="s">
+        <v>52</v>
+      </c>
+      <c r="F49" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>7</v>
       </c>
@@ -1226,8 +1699,14 @@
       <c r="D50">
         <v>136</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E50" t="s">
+        <v>56</v>
+      </c>
+      <c r="F50" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>21</v>
       </c>
@@ -1240,8 +1719,14 @@
       <c r="D51">
         <v>138</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E51" t="s">
+        <v>62</v>
+      </c>
+      <c r="F51" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>9</v>
       </c>
@@ -1254,8 +1739,14 @@
       <c r="D52">
         <v>141</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E52" t="s">
+        <v>47</v>
+      </c>
+      <c r="F52" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>3</v>
       </c>
@@ -1268,8 +1759,14 @@
       <c r="D53">
         <v>116</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E53" t="s">
+        <v>60</v>
+      </c>
+      <c r="F53" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>20</v>
       </c>
@@ -1282,8 +1779,14 @@
       <c r="D54">
         <v>134</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E54" t="s">
+        <v>61</v>
+      </c>
+      <c r="F54" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>30</v>
       </c>
@@ -1296,10 +1799,16 @@
       <c r="D55">
         <v>139</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E55" t="s">
+        <v>57</v>
+      </c>
+      <c r="F55" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="B56">
         <v>0.91</v>
@@ -1310,10 +1819,16 @@
       <c r="D56">
         <v>109</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E56" t="s">
+        <v>63</v>
+      </c>
+      <c r="F56" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="B57">
         <v>0.91</v>
@@ -1324,8 +1839,14 @@
       <c r="D57">
         <v>109</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E57" t="s">
+        <v>63</v>
+      </c>
+      <c r="F57" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>1</v>
       </c>
@@ -1338,8 +1859,14 @@
       <c r="D58">
         <v>110</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E58" t="s">
+        <v>44</v>
+      </c>
+      <c r="F58" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>31</v>
       </c>
@@ -1352,8 +1879,14 @@
       <c r="D59">
         <v>118</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E59" t="s">
+        <v>59</v>
+      </c>
+      <c r="F59" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>32</v>
       </c>
@@ -1366,8 +1899,14 @@
       <c r="D60">
         <v>137</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E60" t="s">
+        <v>64</v>
+      </c>
+      <c r="F60" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>32</v>
       </c>
@@ -1380,13 +1919,15 @@
       <c r="D61">
         <v>137</v>
       </c>
+      <c r="E61" t="s">
+        <v>64</v>
+      </c>
+      <c r="F61" t="s">
+        <v>92</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1" xr:uid="{B19E0F6F-4091-44B6-8908-ADD872FB2D48}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D61">
-      <sortCondition descending="1" ref="B1"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:F1" xr:uid="{B19E0F6F-4091-44B6-8908-ADD872FB2D48}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/HR_factors.xlsx
+++ b/HR_factors.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brend\Documents\GitHub\homerun_model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B5E49C-1ADB-410E-ADD4-636B7CD07F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D47ADF4B-26F2-4D40-AA4B-CA2B4BBE76DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{5F756707-5AD7-439A-B4DC-090231B89164}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$241</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="99">
   <si>
     <t>LAA</t>
   </si>
@@ -327,16 +327,31 @@
   </si>
   <si>
     <t>year</t>
+  </si>
+  <si>
+    <t>zip</t>
+  </si>
+  <si>
+    <t>02215</t>
+  </si>
+  <si>
+    <t>savant_hr</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -362,11 +377,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -701,15 +717,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B19E0F6F-4091-44B6-8908-ADD872FB2D48}">
-  <dimension ref="A1:G181"/>
+  <dimension ref="A1:I241"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="2"/>
+    <col min="9" max="9" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>26</v>
       </c>
@@ -731,79 +749,103 @@
       <c r="G1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B2">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="C2" t="s">
         <v>24</v>
       </c>
       <c r="D2">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="G2">
         <v>2025</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="2">
+        <v>85004</v>
+      </c>
+      <c r="I2">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <v>1.04</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="E3" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="G3">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H3" s="2">
+        <v>85004</v>
+      </c>
+      <c r="I3">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <v>1.02</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="E4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G4">
         <v>2025</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" s="2">
+        <v>85004</v>
+      </c>
+      <c r="I4">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B5">
         <v>1.02</v>
@@ -812,24 +854,30 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="E5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G5">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H5" s="2">
+        <v>85004</v>
+      </c>
+      <c r="I5">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B6">
-        <v>1.04</v>
+        <v>0.9</v>
       </c>
       <c r="C6" t="s">
         <v>24</v>
@@ -844,18 +892,24 @@
         <v>83</v>
       </c>
       <c r="G6">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2023</v>
+      </c>
+      <c r="H6" s="2">
+        <v>85004</v>
+      </c>
+      <c r="I6">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1.02</v>
+        <v>0.9</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7">
         <v>133</v>
@@ -867,56 +921,74 @@
         <v>83</v>
       </c>
       <c r="G7">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2024</v>
+      </c>
+      <c r="H7" s="2">
+        <v>85004</v>
+      </c>
+      <c r="I7">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B8">
-        <v>0.97</v>
+        <v>0.9</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="E8" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="F8" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G8">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2024</v>
+      </c>
+      <c r="H8" s="2">
+        <v>85004</v>
+      </c>
+      <c r="I8">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B9">
-        <v>1.05</v>
+        <v>0.9</v>
       </c>
       <c r="C9" t="s">
         <v>25</v>
       </c>
       <c r="D9">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="F9" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G9">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2023</v>
+      </c>
+      <c r="H9" s="2">
+        <v>85004</v>
+      </c>
+      <c r="I9">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
@@ -936,18 +1008,24 @@
         <v>86</v>
       </c>
       <c r="G10">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2023</v>
+      </c>
+      <c r="H10" s="2">
+        <v>30339</v>
+      </c>
+      <c r="I10">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11">
         <v>144</v>
@@ -961,154 +1039,196 @@
       <c r="G11">
         <v>2025</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H11" s="2">
+        <v>30339</v>
+      </c>
+      <c r="I11">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B12">
-        <v>1.05</v>
+        <v>0.97</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D12">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="E12" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="F12" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="G12">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2023</v>
+      </c>
+      <c r="H12" s="2">
+        <v>30339</v>
+      </c>
+      <c r="I12">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B13">
+        <v>0.99</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13">
+        <v>144</v>
+      </c>
+      <c r="E13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" t="s">
+        <v>86</v>
+      </c>
+      <c r="G13">
+        <v>2024</v>
+      </c>
+      <c r="H13" s="2">
+        <v>30339</v>
+      </c>
+      <c r="I13">
         <v>1.02</v>
       </c>
-      <c r="C13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13">
-        <v>158</v>
-      </c>
-      <c r="E13" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" t="s">
-        <v>73</v>
-      </c>
-      <c r="G13">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B14">
-        <v>0.94</v>
+        <v>0.97</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E14" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F14" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G14">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2024</v>
+      </c>
+      <c r="H14" s="2">
+        <v>30339</v>
+      </c>
+      <c r="I14">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B15">
-        <v>0.94</v>
+        <v>0.99</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D15">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E15" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F15" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G15">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H15" s="2">
+        <v>30339</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16">
         <v>0.97</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D16">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="E16" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F16" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="G16">
         <v>2025</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H16" s="2">
+        <v>30339</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B17">
-        <v>1.01</v>
+        <v>0.97</v>
       </c>
       <c r="C17" t="s">
         <v>25</v>
       </c>
       <c r="D17">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="E17" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="G17">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H17" s="2">
+        <v>30339</v>
+      </c>
+      <c r="I17">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>94</v>
       </c>
       <c r="B18">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D18">
         <v>109</v>
@@ -1120,10 +1240,16 @@
         <v>91</v>
       </c>
       <c r="G18">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H18" s="2">
+        <v>21201</v>
+      </c>
+      <c r="I18">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>94</v>
       </c>
@@ -1145,470 +1271,596 @@
       <c r="G19">
         <v>2025</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H19" s="2">
+        <v>21201</v>
+      </c>
+      <c r="I19">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="B20">
-        <v>1.07</v>
+        <v>0.92</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D20">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="E20" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="F20" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="G20">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2024</v>
+      </c>
+      <c r="H20" s="2">
+        <v>21201</v>
+      </c>
+      <c r="I20">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="B21">
-        <v>1.1200000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="C21" t="s">
         <v>25</v>
       </c>
       <c r="D21">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="E21" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="F21" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="G21">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2023</v>
+      </c>
+      <c r="H21" s="2">
+        <v>21201</v>
+      </c>
+      <c r="I21">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>32</v>
+        <v>94</v>
       </c>
       <c r="B22">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="C22" t="s">
         <v>24</v>
       </c>
       <c r="D22">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="E22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F22" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G22">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2023</v>
+      </c>
+      <c r="H22" s="2">
+        <v>21201</v>
+      </c>
+      <c r="I22">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>94</v>
       </c>
       <c r="B23">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D23">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="E23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G23">
         <v>2025</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H23" s="2">
+        <v>21201</v>
+      </c>
+      <c r="I23">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="B24">
-        <v>1.03</v>
+        <v>0.88</v>
       </c>
       <c r="C24" t="s">
         <v>24</v>
       </c>
       <c r="D24">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E24" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="F24" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="G24">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2024</v>
+      </c>
+      <c r="H24" s="2">
+        <v>21201</v>
+      </c>
+      <c r="I24">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="B25">
-        <v>0.96</v>
+        <v>0.88</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D25">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E25" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="F25" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="G25">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H25" s="2">
+        <v>21201</v>
+      </c>
+      <c r="I25">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B26">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="C26" t="s">
         <v>24</v>
       </c>
       <c r="D26">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="E26" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F26" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="G26">
         <v>2025</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H26" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I26">
+        <v>1.1299999999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B27">
-        <v>0.98</v>
+        <v>1.06</v>
       </c>
       <c r="C27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D27">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="E27" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F27" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="G27">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I27">
+        <v>1.1299999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B28">
+        <v>1.06</v>
+      </c>
+      <c r="C28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28">
+        <v>110</v>
+      </c>
+      <c r="E28" t="s">
+        <v>44</v>
+      </c>
+      <c r="F28" t="s">
+        <v>74</v>
+      </c>
+      <c r="G28">
+        <v>2023</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I28">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B29">
+        <v>1.06</v>
+      </c>
+      <c r="C29" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29">
+        <v>110</v>
+      </c>
+      <c r="E29" t="s">
+        <v>44</v>
+      </c>
+      <c r="F29" t="s">
+        <v>74</v>
+      </c>
+      <c r="G29">
+        <v>2024</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I29">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30">
+        <v>0.94</v>
+      </c>
+      <c r="C30" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30">
+        <v>110</v>
+      </c>
+      <c r="E30" t="s">
+        <v>44</v>
+      </c>
+      <c r="F30" t="s">
+        <v>74</v>
+      </c>
+      <c r="G30">
+        <v>2026</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I30">
         <v>1.01</v>
       </c>
-      <c r="C28" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28">
-        <v>146</v>
-      </c>
-      <c r="E28" t="s">
-        <v>52</v>
-      </c>
-      <c r="F28" t="s">
-        <v>81</v>
-      </c>
-      <c r="G28">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B29">
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B31">
         <v>0.94</v>
       </c>
-      <c r="C29" t="s">
-        <v>25</v>
-      </c>
-      <c r="D29">
-        <v>146</v>
-      </c>
-      <c r="E29" t="s">
-        <v>52</v>
-      </c>
-      <c r="F29" t="s">
-        <v>81</v>
-      </c>
-      <c r="G29">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B30">
-        <v>0.97</v>
-      </c>
-      <c r="C30" t="s">
-        <v>24</v>
-      </c>
-      <c r="D30">
-        <v>121</v>
-      </c>
-      <c r="E30" t="s">
-        <v>50</v>
-      </c>
-      <c r="F30" t="s">
-        <v>68</v>
-      </c>
-      <c r="G30">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B31">
-        <v>1.01</v>
-      </c>
       <c r="C31" t="s">
         <v>25</v>
       </c>
       <c r="D31">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="E31" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F31" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G31">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2023</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I31">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="B32">
-        <v>0.99</v>
+        <v>0.94</v>
       </c>
       <c r="C32" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D32">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E32" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F32" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G32">
         <v>2025</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H32" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I32">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="B33">
-        <v>1.03</v>
+        <v>0.94</v>
       </c>
       <c r="C33" t="s">
         <v>25</v>
       </c>
       <c r="D33">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E33" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F33" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G33">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2024</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I33">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B34">
+        <v>1.01</v>
+      </c>
+      <c r="C34" t="s">
+        <v>25</v>
+      </c>
+      <c r="D34">
+        <v>111</v>
+      </c>
+      <c r="E34" t="s">
+        <v>46</v>
+      </c>
+      <c r="F34" t="s">
+        <v>76</v>
+      </c>
+      <c r="G34">
+        <v>2024</v>
+      </c>
+      <c r="H34" s="2">
+        <v>60616</v>
+      </c>
+      <c r="I34">
         <v>1</v>
       </c>
-      <c r="B34">
-        <v>1.06</v>
-      </c>
-      <c r="C34" t="s">
-        <v>24</v>
-      </c>
-      <c r="D34">
-        <v>110</v>
-      </c>
-      <c r="E34" t="s">
-        <v>44</v>
-      </c>
-      <c r="F34" t="s">
-        <v>74</v>
-      </c>
-      <c r="G34">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B35">
+        <v>1.01</v>
+      </c>
+      <c r="C35" t="s">
+        <v>25</v>
+      </c>
+      <c r="D35">
+        <v>111</v>
+      </c>
+      <c r="E35" t="s">
+        <v>46</v>
+      </c>
+      <c r="F35" t="s">
+        <v>76</v>
+      </c>
+      <c r="G35">
+        <v>2023</v>
+      </c>
+      <c r="H35" s="2">
+        <v>60613</v>
+      </c>
+      <c r="I35">
         <v>1</v>
       </c>
-      <c r="B35">
-        <v>0.94</v>
-      </c>
-      <c r="C35" t="s">
-        <v>25</v>
-      </c>
-      <c r="D35">
-        <v>110</v>
-      </c>
-      <c r="E35" t="s">
-        <v>44</v>
-      </c>
-      <c r="F35" t="s">
-        <v>74</v>
-      </c>
-      <c r="G35">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B36">
+        <v>0.95</v>
+      </c>
+      <c r="C36" t="s">
+        <v>24</v>
+      </c>
+      <c r="D36">
+        <v>111</v>
+      </c>
+      <c r="E36" t="s">
+        <v>46</v>
+      </c>
+      <c r="F36" t="s">
+        <v>76</v>
+      </c>
+      <c r="G36">
+        <v>2023</v>
+      </c>
+      <c r="H36" s="2">
+        <v>60613</v>
+      </c>
+      <c r="I36">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B37">
+        <v>0.95</v>
+      </c>
+      <c r="C37" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37">
+        <v>111</v>
+      </c>
+      <c r="E37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F37" t="s">
+        <v>76</v>
+      </c>
+      <c r="G37">
+        <v>2024</v>
+      </c>
+      <c r="H37" s="2">
+        <v>60616</v>
+      </c>
+      <c r="I37">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B38">
         <v>1.01</v>
       </c>
-      <c r="C36" t="s">
-        <v>24</v>
-      </c>
-      <c r="D36">
-        <v>135</v>
-      </c>
-      <c r="E36" t="s">
-        <v>51</v>
-      </c>
-      <c r="F36" t="s">
-        <v>80</v>
-      </c>
-      <c r="G36">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B37">
-        <v>1</v>
-      </c>
-      <c r="C37" t="s">
-        <v>25</v>
-      </c>
-      <c r="D37">
-        <v>135</v>
-      </c>
-      <c r="E37" t="s">
-        <v>51</v>
-      </c>
-      <c r="F37" t="s">
-        <v>80</v>
-      </c>
-      <c r="G37">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B38">
-        <v>1.08</v>
-      </c>
       <c r="C38" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D38">
-        <v>143</v>
+        <v>111</v>
       </c>
       <c r="E38" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F38" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G38">
         <v>2025</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H38" s="2">
+        <v>60613</v>
+      </c>
+      <c r="I38">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B39">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="C39" t="s">
         <v>25</v>
       </c>
       <c r="D39">
-        <v>143</v>
+        <v>111</v>
       </c>
       <c r="E39" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F39" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G39">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H39" s="2">
+        <v>60613</v>
+      </c>
+      <c r="I39">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B40">
         <v>0.95</v>
@@ -1617,734 +1869,926 @@
         <v>24</v>
       </c>
       <c r="D40">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="E40" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="F40" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="G40">
         <v>2025</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H40" s="2">
+        <v>60613</v>
+      </c>
+      <c r="I40">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B41">
+        <v>0.95</v>
+      </c>
+      <c r="C41" t="s">
+        <v>24</v>
+      </c>
+      <c r="D41">
+        <v>111</v>
+      </c>
+      <c r="E41" t="s">
+        <v>46</v>
+      </c>
+      <c r="F41" t="s">
+        <v>76</v>
+      </c>
+      <c r="G41">
+        <v>2026</v>
+      </c>
+      <c r="H41" s="2">
+        <v>60613</v>
+      </c>
+      <c r="I41">
         <v>0.91</v>
       </c>
-      <c r="C41" t="s">
-        <v>25</v>
-      </c>
-      <c r="D41">
-        <v>134</v>
-      </c>
-      <c r="E41" t="s">
-        <v>61</v>
-      </c>
-      <c r="F41" t="s">
-        <v>89</v>
-      </c>
-      <c r="G41">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B42">
-        <v>1.05</v>
+        <v>0.97</v>
       </c>
       <c r="C42" t="s">
         <v>24</v>
       </c>
       <c r="D42">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="E42" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F42" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G42">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2023</v>
+      </c>
+      <c r="H42" s="2">
+        <v>60616</v>
+      </c>
+      <c r="I42">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B43">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="C43" t="s">
         <v>25</v>
       </c>
       <c r="D43">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="E43" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F43" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G43">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2023</v>
+      </c>
+      <c r="H43" s="2">
+        <v>60616</v>
+      </c>
+      <c r="I43">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="C44" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D44">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="E44" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F44" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="G44">
         <v>2025</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H44" s="2">
+        <v>60616</v>
+      </c>
+      <c r="I44">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="B45">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="C45" t="s">
         <v>25</v>
       </c>
       <c r="D45">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="E45" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F45" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="G45">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H45" s="2">
+        <v>60616</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B46">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="C46" t="s">
         <v>24</v>
       </c>
       <c r="D46">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E46" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F46" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G46">
         <v>2025</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H46" s="2">
+        <v>60616</v>
+      </c>
+      <c r="I46">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B47">
+        <v>0.97</v>
+      </c>
+      <c r="C47" t="s">
+        <v>24</v>
+      </c>
+      <c r="D47">
+        <v>112</v>
+      </c>
+      <c r="E47" t="s">
+        <v>54</v>
+      </c>
+      <c r="F47" t="s">
+        <v>70</v>
+      </c>
+      <c r="G47">
+        <v>2026</v>
+      </c>
+      <c r="H47" s="2">
+        <v>60616</v>
+      </c>
+      <c r="I47">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B48">
         <v>1.01</v>
       </c>
-      <c r="C47" t="s">
-        <v>25</v>
-      </c>
-      <c r="D47">
-        <v>111</v>
-      </c>
-      <c r="E47" t="s">
-        <v>46</v>
-      </c>
-      <c r="F47" t="s">
-        <v>76</v>
-      </c>
-      <c r="G47">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
+      <c r="C48" t="s">
+        <v>25</v>
+      </c>
+      <c r="D48">
+        <v>112</v>
+      </c>
+      <c r="E48" t="s">
+        <v>54</v>
+      </c>
+      <c r="F48" t="s">
+        <v>70</v>
+      </c>
+      <c r="G48">
+        <v>2024</v>
+      </c>
+      <c r="H48" s="2">
+        <v>60613</v>
+      </c>
+      <c r="I48">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B49">
+        <v>0.97</v>
+      </c>
+      <c r="C49" t="s">
+        <v>24</v>
+      </c>
+      <c r="D49">
+        <v>112</v>
+      </c>
+      <c r="E49" t="s">
+        <v>54</v>
+      </c>
+      <c r="F49" t="s">
+        <v>70</v>
+      </c>
+      <c r="G49">
+        <v>2024</v>
+      </c>
+      <c r="H49" s="2">
+        <v>60613</v>
+      </c>
+      <c r="I49">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B48">
+      <c r="B50">
         <v>1.17</v>
       </c>
-      <c r="C48" t="s">
-        <v>24</v>
-      </c>
-      <c r="D48">
+      <c r="C50" t="s">
+        <v>24</v>
+      </c>
+      <c r="D50">
         <v>113</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E50" t="s">
         <v>35</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F50" t="s">
         <v>66</v>
       </c>
-      <c r="G48">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
+      <c r="G50">
+        <v>2024</v>
+      </c>
+      <c r="H50" s="2">
+        <v>45202</v>
+      </c>
+      <c r="I50">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B49">
+      <c r="B51">
+        <v>1.17</v>
+      </c>
+      <c r="C51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D51">
+        <v>113</v>
+      </c>
+      <c r="E51" t="s">
+        <v>35</v>
+      </c>
+      <c r="F51" t="s">
+        <v>66</v>
+      </c>
+      <c r="G51">
+        <v>2023</v>
+      </c>
+      <c r="H51" s="2">
+        <v>45202</v>
+      </c>
+      <c r="I51">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52">
         <v>1.1399999999999999</v>
       </c>
-      <c r="C49" t="s">
-        <v>25</v>
-      </c>
-      <c r="D49">
+      <c r="C52" t="s">
+        <v>25</v>
+      </c>
+      <c r="D52">
         <v>113</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E52" t="s">
         <v>35</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F52" t="s">
         <v>66</v>
       </c>
-      <c r="G49">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B50">
-        <v>1.05</v>
-      </c>
-      <c r="C50" t="s">
-        <v>24</v>
-      </c>
-      <c r="D50">
-        <v>115</v>
-      </c>
-      <c r="E50" t="s">
-        <v>38</v>
-      </c>
-      <c r="F50" t="s">
-        <v>69</v>
-      </c>
-      <c r="G50">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B51">
-        <v>1.08</v>
-      </c>
-      <c r="C51" t="s">
-        <v>25</v>
-      </c>
-      <c r="D51">
-        <v>115</v>
-      </c>
-      <c r="E51" t="s">
-        <v>38</v>
-      </c>
-      <c r="F51" t="s">
-        <v>69</v>
-      </c>
-      <c r="G51">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B52">
-        <v>0.92</v>
-      </c>
-      <c r="C52" t="s">
-        <v>24</v>
-      </c>
-      <c r="D52">
-        <v>118</v>
-      </c>
-      <c r="E52" t="s">
-        <v>59</v>
-      </c>
-      <c r="F52" t="s">
-        <v>87</v>
-      </c>
       <c r="G52">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2023</v>
+      </c>
+      <c r="H52" s="2">
+        <v>45202</v>
+      </c>
+      <c r="I52">
+        <v>1.1299999999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B53">
-        <v>0.96</v>
+        <v>1.17</v>
       </c>
       <c r="C53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D53">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E53" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="F53" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="G53">
         <v>2025</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H53" s="2">
+        <v>45202</v>
+      </c>
+      <c r="I53">
+        <v>1.1299999999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B54">
-        <v>0.95</v>
+        <v>1.17</v>
       </c>
       <c r="C54" t="s">
         <v>24</v>
       </c>
       <c r="D54">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E54" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="F54" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="G54">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H54" s="2">
+        <v>45202</v>
+      </c>
+      <c r="I54">
+        <v>1.1299999999999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B55">
-        <v>0.98</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="C55" t="s">
         <v>25</v>
       </c>
       <c r="D55">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E55" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="F55" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="G55">
         <v>2025</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H55" s="2">
+        <v>45202</v>
+      </c>
+      <c r="I55">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B56">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="C56" t="s">
+        <v>25</v>
+      </c>
+      <c r="D56">
+        <v>113</v>
+      </c>
+      <c r="E56" t="s">
+        <v>35</v>
+      </c>
+      <c r="F56" t="s">
+        <v>66</v>
+      </c>
+      <c r="G56">
+        <v>2024</v>
+      </c>
+      <c r="H56" s="2">
+        <v>45202</v>
+      </c>
+      <c r="I56">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B57">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="C57" t="s">
+        <v>25</v>
+      </c>
+      <c r="D57">
+        <v>113</v>
+      </c>
+      <c r="E57" t="s">
+        <v>35</v>
+      </c>
+      <c r="F57" t="s">
+        <v>66</v>
+      </c>
+      <c r="G57">
+        <v>2026</v>
+      </c>
+      <c r="H57" s="2">
+        <v>45202</v>
+      </c>
+      <c r="I57">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B58">
+        <v>1.03</v>
+      </c>
+      <c r="C58" t="s">
+        <v>24</v>
+      </c>
+      <c r="D58">
+        <v>114</v>
+      </c>
+      <c r="E58" t="s">
+        <v>45</v>
+      </c>
+      <c r="F58" t="s">
+        <v>75</v>
+      </c>
+      <c r="G58">
+        <v>2026</v>
+      </c>
+      <c r="H58" s="2">
+        <v>44115</v>
+      </c>
+      <c r="I58">
         <v>1.02</v>
       </c>
-      <c r="C56" t="s">
-        <v>24</v>
-      </c>
-      <c r="D56">
-        <v>142</v>
-      </c>
-      <c r="E56" t="s">
-        <v>48</v>
-      </c>
-      <c r="F56" t="s">
-        <v>78</v>
-      </c>
-      <c r="G56">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B57">
-        <v>0.96</v>
-      </c>
-      <c r="C57" t="s">
-        <v>25</v>
-      </c>
-      <c r="D57">
-        <v>142</v>
-      </c>
-      <c r="E57" t="s">
-        <v>48</v>
-      </c>
-      <c r="F57" t="s">
-        <v>78</v>
-      </c>
-      <c r="G57">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B58">
-        <v>1.08</v>
-      </c>
-      <c r="C58" t="s">
-        <v>24</v>
-      </c>
-      <c r="D58">
-        <v>145</v>
-      </c>
-      <c r="E58" t="s">
-        <v>39</v>
-      </c>
-      <c r="F58" t="s">
-        <v>70</v>
-      </c>
-      <c r="G58">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="B59">
         <v>1.03</v>
       </c>
       <c r="C59" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D59">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="E59" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F59" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G59">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2024</v>
+      </c>
+      <c r="H59" s="2">
+        <v>44115</v>
+      </c>
+      <c r="I59">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B60">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="C60" t="s">
         <v>24</v>
       </c>
       <c r="D60">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="E60" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="F60" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G60">
         <v>2025</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H60" s="2">
+        <v>44115</v>
+      </c>
+      <c r="I60">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B61">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="C61" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D61">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="E61" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="F61" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G61">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2023</v>
+      </c>
+      <c r="H61" s="2">
+        <v>44115</v>
+      </c>
+      <c r="I61">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B62">
-        <v>1.07</v>
+        <v>0.96</v>
       </c>
       <c r="C62" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D62">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E62" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F62" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="G62">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2023</v>
+      </c>
+      <c r="H62" s="2">
+        <v>44115</v>
+      </c>
+      <c r="I62">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B63">
-        <v>1.04</v>
+        <v>0.96</v>
       </c>
       <c r="C63" t="s">
         <v>25</v>
       </c>
       <c r="D63">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E63" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F63" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="G63">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H63" s="2">
+        <v>44115</v>
+      </c>
+      <c r="I63">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="B64">
-        <v>1.02</v>
+        <v>0.96</v>
       </c>
       <c r="C64" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D64">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E64" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F64" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G64">
         <v>2024</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H64" s="2">
+        <v>44115</v>
+      </c>
+      <c r="I64">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="B65">
-        <v>1.02</v>
+        <v>0.96</v>
       </c>
       <c r="C65" t="s">
         <v>25</v>
       </c>
       <c r="D65">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E65" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F65" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G65">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+      <c r="H65" s="2">
+        <v>44115</v>
+      </c>
+      <c r="I65">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B66">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="C66" t="s">
         <v>24</v>
       </c>
       <c r="D66">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="E66" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F66" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G66">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H66" s="2">
+        <v>80205</v>
+      </c>
+      <c r="I66">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B67">
-        <v>0.9</v>
+        <v>1.08</v>
       </c>
       <c r="C67" t="s">
         <v>25</v>
       </c>
       <c r="D67">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="E67" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F67" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G67">
         <v>2024</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H67" s="2">
+        <v>80205</v>
+      </c>
+      <c r="I67">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B68">
-        <v>0.97</v>
+        <v>1.08</v>
       </c>
       <c r="C68" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D68">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="E68" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F68" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="G68">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2023</v>
+      </c>
+      <c r="H68" s="2">
+        <v>80205</v>
+      </c>
+      <c r="I68">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B69">
+        <v>1.08</v>
+      </c>
+      <c r="C69" t="s">
+        <v>25</v>
+      </c>
+      <c r="D69">
+        <v>115</v>
+      </c>
+      <c r="E69" t="s">
+        <v>38</v>
+      </c>
+      <c r="F69" t="s">
+        <v>69</v>
+      </c>
+      <c r="G69">
+        <v>2025</v>
+      </c>
+      <c r="H69" s="2">
+        <v>80205</v>
+      </c>
+      <c r="I69">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B70">
         <v>1.05</v>
       </c>
-      <c r="C69" t="s">
-        <v>25</v>
-      </c>
-      <c r="D69">
-        <v>141</v>
-      </c>
-      <c r="E69" t="s">
-        <v>47</v>
-      </c>
-      <c r="F69" t="s">
-        <v>77</v>
-      </c>
-      <c r="G69">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B70">
-        <v>0.99</v>
-      </c>
       <c r="C70" t="s">
         <v>24</v>
       </c>
       <c r="D70">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="E70" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F70" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="G70">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+      <c r="H70" s="2">
+        <v>80205</v>
+      </c>
+      <c r="I70">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B71">
-        <v>0.97</v>
+        <v>1.08</v>
       </c>
       <c r="C71" t="s">
         <v>25</v>
       </c>
       <c r="D71">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="E71" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F71" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="G71">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H71" s="2">
+        <v>80205</v>
+      </c>
+      <c r="I71">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B72">
         <v>1.05</v>
@@ -2353,102 +2797,126 @@
         <v>24</v>
       </c>
       <c r="D72">
-        <v>158</v>
+        <v>115</v>
       </c>
       <c r="E72" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F72" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G72">
         <v>2024</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H72" s="2">
+        <v>80205</v>
+      </c>
+      <c r="I72">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B73">
+        <v>1.05</v>
+      </c>
+      <c r="C73" t="s">
+        <v>24</v>
+      </c>
+      <c r="D73">
+        <v>115</v>
+      </c>
+      <c r="E73" t="s">
+        <v>38</v>
+      </c>
+      <c r="F73" t="s">
+        <v>69</v>
+      </c>
+      <c r="G73">
+        <v>2023</v>
+      </c>
+      <c r="H73" s="2">
+        <v>80205</v>
+      </c>
+      <c r="I73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B74">
+        <v>1.03</v>
+      </c>
+      <c r="C74" t="s">
+        <v>25</v>
+      </c>
+      <c r="D74">
+        <v>145</v>
+      </c>
+      <c r="E74" t="s">
+        <v>39</v>
+      </c>
+      <c r="F74" t="s">
+        <v>70</v>
+      </c>
+      <c r="G74">
+        <v>2023</v>
+      </c>
+      <c r="H74" s="2">
+        <v>48201</v>
+      </c>
+      <c r="I74">
         <v>1.02</v>
       </c>
-      <c r="C73" t="s">
-        <v>25</v>
-      </c>
-      <c r="D73">
-        <v>158</v>
-      </c>
-      <c r="E73" t="s">
-        <v>43</v>
-      </c>
-      <c r="F73" t="s">
-        <v>73</v>
-      </c>
-      <c r="G73">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B74">
-        <v>0.94</v>
-      </c>
-      <c r="C74" t="s">
-        <v>24</v>
-      </c>
-      <c r="D74">
-        <v>138</v>
-      </c>
-      <c r="E74" t="s">
-        <v>62</v>
-      </c>
-      <c r="F74" t="s">
-        <v>90</v>
-      </c>
-      <c r="G74">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B75">
-        <v>0.94</v>
+        <v>1.08</v>
       </c>
       <c r="C75" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D75">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="E75" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="F75" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="G75">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2023</v>
+      </c>
+      <c r="H75" s="2">
+        <v>48201</v>
+      </c>
+      <c r="I75">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="B76">
-        <v>0.97</v>
+        <v>1.03</v>
       </c>
       <c r="C76" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D76">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="E76" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F76" t="s">
         <v>70</v>
@@ -2456,240 +2924,306 @@
       <c r="G76">
         <v>2024</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H76" s="2">
+        <v>48201</v>
+      </c>
+      <c r="I76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="B77">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="C77" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D77">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="E77" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F77" t="s">
         <v>70</v>
       </c>
       <c r="G77">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H77" s="2">
+        <v>48201</v>
+      </c>
+      <c r="I77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="B78">
-        <v>0.88</v>
+        <v>1.03</v>
       </c>
       <c r="C78" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D78">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="E78" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="F78" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="G78">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+      <c r="H78" s="2">
+        <v>48201</v>
+      </c>
+      <c r="I78">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="B79">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="C79" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D79">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="E79" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="F79" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="G79">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+      <c r="H79" s="2">
+        <v>48201</v>
+      </c>
+      <c r="I79">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="B80">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="C80" t="s">
         <v>24</v>
       </c>
       <c r="D80">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="E80" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F80" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G80">
         <v>2024</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H80" s="2">
+        <v>48201</v>
+      </c>
+      <c r="I80">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="B81">
-        <v>1.1200000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="C81" t="s">
         <v>25</v>
       </c>
       <c r="D81">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="E81" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F81" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G81">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H81" s="2">
+        <v>48201</v>
+      </c>
+      <c r="I81">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="B82">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="C82" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D82">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="E82" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F82" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G82">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H82" s="2">
+        <v>77002</v>
+      </c>
+      <c r="I82">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="B83">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="C83" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D83">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="E83" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F83" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G83">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H83" s="2">
+        <v>77002</v>
+      </c>
+      <c r="I83">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B84">
-        <v>1.03</v>
+        <v>0.98</v>
       </c>
       <c r="C84" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D84">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E84" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F84" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="G84">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+      <c r="H84" s="2">
+        <v>77002</v>
+      </c>
+      <c r="I84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B85">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="C85" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D85">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E85" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F85" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="G85">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+      <c r="H85" s="2">
+        <v>77002</v>
+      </c>
+      <c r="I85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B86">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="C86" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D86">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="E86" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F86" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G86">
         <v>2024</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H86" s="2">
+        <v>77002</v>
+      </c>
+      <c r="I86">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B87">
         <v>0.98</v>
@@ -2698,389 +3232,491 @@
         <v>25</v>
       </c>
       <c r="D87">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="E87" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F87" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G87">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2023</v>
+      </c>
+      <c r="H87" s="2">
+        <v>77002</v>
+      </c>
+      <c r="I87">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B88">
-        <v>1.01</v>
+        <v>0.95</v>
       </c>
       <c r="C88" t="s">
         <v>24</v>
       </c>
       <c r="D88">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="E88" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F88" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G88">
         <v>2024</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H88" s="2">
+        <v>77002</v>
+      </c>
+      <c r="I88">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B89">
-        <v>0.94</v>
+        <v>0.95</v>
       </c>
       <c r="C89" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D89">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="E89" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F89" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G89">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2023</v>
+      </c>
+      <c r="H89" s="2">
+        <v>77002</v>
+      </c>
+      <c r="I89">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B90">
-        <v>0.97</v>
+        <v>1.02</v>
       </c>
       <c r="C90" t="s">
         <v>24</v>
       </c>
       <c r="D90">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E90" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F90" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G90">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H90" s="2">
+        <v>64129</v>
+      </c>
+      <c r="I90">
+        <v>1.1299999999999999</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B91">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="C91" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D91">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E91" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F91" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G91">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+      <c r="H91" s="2">
+        <v>64129</v>
+      </c>
+      <c r="I91">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B92">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="C92" t="s">
         <v>24</v>
       </c>
       <c r="D92">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E92" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F92" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G92">
         <v>2024</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H92" s="2">
+        <v>64129</v>
+      </c>
+      <c r="I92">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B93">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="C93" t="s">
         <v>25</v>
       </c>
       <c r="D93">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E93" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F93" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G93">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H93" s="2">
+        <v>64129</v>
+      </c>
+      <c r="I93">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="B94">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="C94" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D94">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="E94" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F94" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G94">
         <v>2024</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H94" s="2">
+        <v>64129</v>
+      </c>
+      <c r="I94">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="B95">
-        <v>0.94</v>
+        <v>1.02</v>
       </c>
       <c r="C95" t="s">
         <v>25</v>
       </c>
       <c r="D95">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="E95" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F95" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G95">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+      <c r="H95" s="2">
+        <v>64129</v>
+      </c>
+      <c r="I95">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="B96">
+        <v>1.02</v>
+      </c>
+      <c r="C96" t="s">
+        <v>25</v>
+      </c>
+      <c r="D96">
+        <v>117</v>
+      </c>
+      <c r="E96" t="s">
+        <v>53</v>
+      </c>
+      <c r="F96" t="s">
+        <v>82</v>
+      </c>
+      <c r="G96">
+        <v>2023</v>
+      </c>
+      <c r="H96" s="2">
+        <v>64129</v>
+      </c>
+      <c r="I96">
         <v>1.01</v>
       </c>
-      <c r="C96" t="s">
-        <v>24</v>
-      </c>
-      <c r="D96">
-        <v>135</v>
-      </c>
-      <c r="E96" t="s">
-        <v>51</v>
-      </c>
-      <c r="F96" t="s">
-        <v>80</v>
-      </c>
-      <c r="G96">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="B97">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="C97" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D97">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="E97" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F97" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G97">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2023</v>
+      </c>
+      <c r="H97" s="2">
+        <v>64129</v>
+      </c>
+      <c r="I97">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B98">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="C98" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D98">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="E98" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="F98" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="G98">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+      <c r="H98" s="2">
+        <v>92806</v>
+      </c>
+      <c r="I98">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B99">
-        <v>1.04</v>
+        <v>0.96</v>
       </c>
       <c r="C99" t="s">
         <v>25</v>
       </c>
       <c r="D99">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="E99" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="F99" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="G99">
         <v>2024</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H99" s="2">
+        <v>90012</v>
+      </c>
+      <c r="I99">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B100">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="C100" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D100">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="E100" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F100" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G100">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2023</v>
+      </c>
+      <c r="H100" s="2">
+        <v>92806</v>
+      </c>
+      <c r="I100">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B101">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="C101" t="s">
         <v>25</v>
       </c>
       <c r="D101">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="E101" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F101" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G101">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H101" s="2">
+        <v>92806</v>
+      </c>
+      <c r="I101">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="B102">
-        <v>1.05</v>
+        <v>0.92</v>
       </c>
       <c r="C102" t="s">
         <v>24</v>
       </c>
       <c r="D102">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="E102" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="F102" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="G102">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2023</v>
+      </c>
+      <c r="H102" s="2">
+        <v>92806</v>
+      </c>
+      <c r="I102">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="B103">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="C103" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D103">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="E103" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="F103" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="G103">
         <v>2024</v>
       </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H103" s="2">
+        <v>90012</v>
+      </c>
+      <c r="I103">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B104">
         <v>0.92</v>
@@ -3089,366 +3725,462 @@
         <v>24</v>
       </c>
       <c r="D104">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="E104" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F104" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G104">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H104" s="2">
+        <v>92806</v>
+      </c>
+      <c r="I104">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B105">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="C105" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D105">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="E105" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F105" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G105">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+      <c r="H105" s="2">
+        <v>92806</v>
+      </c>
+      <c r="I105">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="B106">
-        <v>0.95</v>
+        <v>1.07</v>
       </c>
       <c r="C106" t="s">
         <v>24</v>
       </c>
       <c r="D106">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E106" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F106" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="G106">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2023</v>
+      </c>
+      <c r="H106" s="2">
+        <v>90012</v>
+      </c>
+      <c r="I106">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="B107">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="C107" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D107">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E107" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F107" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="G107">
         <v>2024</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H107" s="2">
+        <v>92806</v>
+      </c>
+      <c r="I107">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B108">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="C108" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D108">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E108" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F108" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G108">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+      <c r="H108" s="2">
+        <v>90012</v>
+      </c>
+      <c r="I108">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B109">
-        <v>1.1399999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="C109" t="s">
         <v>25</v>
       </c>
       <c r="D109">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E109" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F109" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G109">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H109" s="2">
+        <v>90012</v>
+      </c>
+      <c r="I109">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="B110">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="C110" t="s">
         <v>24</v>
       </c>
       <c r="D110">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E110" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F110" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G110">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+      <c r="H110" s="2">
+        <v>90012</v>
+      </c>
+      <c r="I110">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="B111">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="C111" t="s">
         <v>25</v>
       </c>
       <c r="D111">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E111" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F111" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G111">
         <v>2024</v>
       </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H111" s="2">
+        <v>92806</v>
+      </c>
+      <c r="I111">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="B112">
-        <v>0.92</v>
+        <v>1.04</v>
       </c>
       <c r="C112" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D112">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="E112" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="F112" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="G112">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2023</v>
+      </c>
+      <c r="H112" s="2">
+        <v>90012</v>
+      </c>
+      <c r="I112">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="B113">
-        <v>0.96</v>
+        <v>1.07</v>
       </c>
       <c r="C113" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D113">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="E113" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="F113" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="G113">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H113" s="2">
+        <v>90012</v>
+      </c>
+      <c r="I113">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B114">
-        <v>0.95</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="C114" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D114">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E114" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="F114" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="G114">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H114" s="2">
+        <v>33125</v>
+      </c>
+      <c r="I114">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B115">
-        <v>0.98</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="C115" t="s">
         <v>25</v>
       </c>
       <c r="D115">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E115" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="F115" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="G115">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+      <c r="H115" s="2">
+        <v>33125</v>
+      </c>
+      <c r="I115">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B116">
-        <v>1.02</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="C116" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D116">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="E116" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F116" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="G116">
         <v>2024</v>
       </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H116" s="2">
+        <v>33125</v>
+      </c>
+      <c r="I116">
+        <v>1.1299999999999999</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B117">
-        <v>0.96</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="C117" t="s">
         <v>25</v>
       </c>
       <c r="D117">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="E117" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F117" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="G117">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2023</v>
+      </c>
+      <c r="H117" s="2">
+        <v>33125</v>
+      </c>
+      <c r="I117">
+        <v>1.1299999999999999</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B118">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="C118" t="s">
         <v>24</v>
       </c>
       <c r="D118">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="E118" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F118" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G118">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H118" s="2">
+        <v>33125</v>
+      </c>
+      <c r="I118">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B119">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="C119" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D119">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="E119" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F119" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G119">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+      <c r="H119" s="2">
+        <v>33125</v>
+      </c>
+      <c r="I119">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B120">
         <v>1.07</v>
@@ -3457,280 +4189,352 @@
         <v>24</v>
       </c>
       <c r="D120">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="E120" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F120" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G120">
         <v>2024</v>
       </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H120" s="2">
+        <v>33125</v>
+      </c>
+      <c r="I120">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B121">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="C121" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D121">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="E121" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F121" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G121">
+        <v>2023</v>
+      </c>
+      <c r="H121" s="2">
+        <v>33125</v>
+      </c>
+      <c r="I121">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B122">
+        <v>1.01</v>
+      </c>
+      <c r="C122" t="s">
+        <v>24</v>
+      </c>
+      <c r="D122">
+        <v>146</v>
+      </c>
+      <c r="E122" t="s">
+        <v>52</v>
+      </c>
+      <c r="F122" t="s">
+        <v>81</v>
+      </c>
+      <c r="G122">
         <v>2024</v>
       </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A122" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B122">
-        <v>1.07</v>
-      </c>
-      <c r="C122" t="s">
-        <v>24</v>
-      </c>
-      <c r="D122">
-        <v>108</v>
-      </c>
-      <c r="E122" t="s">
-        <v>40</v>
-      </c>
-      <c r="F122" t="s">
-        <v>67</v>
-      </c>
-      <c r="G122">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H122" s="2">
+        <v>53214</v>
+      </c>
+      <c r="I122">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="B123">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="C123" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D123">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="E123" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F123" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="G123">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+      <c r="H123" s="2">
+        <v>53214</v>
+      </c>
+      <c r="I123">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B124">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="C124" t="s">
         <v>24</v>
       </c>
       <c r="D124">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="E124" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F124" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G124">
         <v>2023</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H124" s="2">
+        <v>53214</v>
+      </c>
+      <c r="I124">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B125">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="C125" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D125">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="E125" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F125" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G125">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H125" s="2">
+        <v>53214</v>
+      </c>
+      <c r="I125">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B126">
-        <v>0.9</v>
+        <v>0.94</v>
       </c>
       <c r="C126" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D126">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="E126" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F126" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G126">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2024</v>
+      </c>
+      <c r="H126" s="2">
+        <v>53214</v>
+      </c>
+      <c r="I126">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B127">
-        <v>0.9</v>
+        <v>0.94</v>
       </c>
       <c r="C127" t="s">
         <v>25</v>
       </c>
       <c r="D127">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="E127" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F127" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G127">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H127" s="2">
+        <v>53214</v>
+      </c>
+      <c r="I127">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B128">
-        <v>0.97</v>
+        <v>0.94</v>
       </c>
       <c r="C128" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D128">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E128" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F128" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G128">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+      <c r="H128" s="2">
+        <v>53214</v>
+      </c>
+      <c r="I128">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B129">
-        <v>1.05</v>
+        <v>0.94</v>
       </c>
       <c r="C129" t="s">
         <v>25</v>
       </c>
       <c r="D129">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E129" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F129" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G129">
         <v>2023</v>
       </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H129" s="2">
+        <v>53214</v>
+      </c>
+      <c r="I129">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B130">
-        <v>0.99</v>
+        <v>1.05</v>
       </c>
       <c r="C130" t="s">
         <v>24</v>
       </c>
       <c r="D130">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="E130" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="F130" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="G130">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2024</v>
+      </c>
+      <c r="H130" s="2">
+        <v>55403</v>
+      </c>
+      <c r="I130">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B131">
-        <v>0.97</v>
+        <v>1.02</v>
       </c>
       <c r="C131" t="s">
         <v>25</v>
       </c>
       <c r="D131">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="E131" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="F131" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="G131">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+      <c r="H131" s="2">
+        <v>55403</v>
+      </c>
+      <c r="I131">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B132">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="C132" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D132">
         <v>158</v>
@@ -3742,10 +4546,16 @@
         <v>73</v>
       </c>
       <c r="G132">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2024</v>
+      </c>
+      <c r="H132" s="2">
+        <v>55403</v>
+      </c>
+      <c r="I132">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>17</v>
       </c>
@@ -3765,265 +4575,337 @@
         <v>73</v>
       </c>
       <c r="G133">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H133" s="2">
+        <v>55403</v>
+      </c>
+      <c r="I133">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B134">
-        <v>0.94</v>
+        <v>1.05</v>
       </c>
       <c r="C134" t="s">
         <v>24</v>
       </c>
       <c r="D134">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="E134" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="F134" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="G134">
         <v>2023</v>
       </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H134" s="2">
+        <v>55403</v>
+      </c>
+      <c r="I134">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B135">
-        <v>0.94</v>
+        <v>1.02</v>
       </c>
       <c r="C135" t="s">
         <v>25</v>
       </c>
       <c r="D135">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="E135" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="F135" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="G135">
         <v>2023</v>
       </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H135" s="2">
+        <v>55403</v>
+      </c>
+      <c r="I135">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B136">
-        <v>0.97</v>
+        <v>1.05</v>
       </c>
       <c r="C136" t="s">
         <v>24</v>
       </c>
       <c r="D136">
-        <v>112</v>
+        <v>158</v>
       </c>
       <c r="E136" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="F136" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G136">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+      <c r="H136" s="2">
+        <v>55403</v>
+      </c>
+      <c r="I136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B137">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="C137" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D137">
-        <v>112</v>
+        <v>158</v>
       </c>
       <c r="E137" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="F137" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G137">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H137" s="2">
+        <v>55403</v>
+      </c>
+      <c r="I137">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="B138">
-        <v>0.88</v>
+        <v>0.96</v>
       </c>
       <c r="C138" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D138">
-        <v>109</v>
+        <v>142</v>
       </c>
       <c r="E138" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="F138" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G138">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2024</v>
+      </c>
+      <c r="H138" s="2">
+        <v>10451</v>
+      </c>
+      <c r="I138">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="B139">
-        <v>0.92</v>
+        <v>1.02</v>
       </c>
       <c r="C139" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D139">
-        <v>109</v>
+        <v>142</v>
       </c>
       <c r="E139" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="F139" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G139">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2024</v>
+      </c>
+      <c r="H139" s="2">
+        <v>10451</v>
+      </c>
+      <c r="I139">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B140">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="C140" t="s">
         <v>24</v>
       </c>
       <c r="D140">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="E140" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F140" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="G140">
         <v>2023</v>
       </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H140" s="2">
+        <v>11368</v>
+      </c>
+      <c r="I140">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B141">
-        <v>1.1200000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="C141" t="s">
         <v>25</v>
       </c>
       <c r="D141">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="E141" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F141" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="G141">
         <v>2023</v>
       </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H141" s="2">
+        <v>11368</v>
+      </c>
+      <c r="I141">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="B142">
-        <v>0.91</v>
+        <v>1.02</v>
       </c>
       <c r="C142" t="s">
         <v>24</v>
       </c>
       <c r="D142">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E142" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F142" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="G142">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+      <c r="H142" s="2">
+        <v>11368</v>
+      </c>
+      <c r="I142">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="B143">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="C143" t="s">
         <v>25</v>
       </c>
       <c r="D143">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E143" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F143" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="G143">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+      <c r="H143" s="2">
+        <v>11368</v>
+      </c>
+      <c r="I143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B144">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="C144" t="s">
         <v>24</v>
       </c>
       <c r="D144">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="E144" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F144" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G144">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H144" s="2">
+        <v>11368</v>
+      </c>
+      <c r="I144">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B145">
         <v>0.96</v>
@@ -4032,111 +4914,141 @@
         <v>25</v>
       </c>
       <c r="D145">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="E145" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F145" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G145">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H145" s="2">
+        <v>11368</v>
+      </c>
+      <c r="I145">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B146">
-        <v>0.93</v>
+        <v>1.01</v>
       </c>
       <c r="C146" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D146">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="E146" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F146" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="G146">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+      <c r="H146" s="2">
+        <v>10451</v>
+      </c>
+      <c r="I146">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B147">
-        <v>0.98</v>
+        <v>1.01</v>
       </c>
       <c r="C147" t="s">
         <v>25</v>
       </c>
       <c r="D147">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="E147" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F147" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="G147">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H147" s="2">
+        <v>10451</v>
+      </c>
+      <c r="I147">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B148">
         <v>1.01</v>
       </c>
       <c r="C148" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D148">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="E148" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F148" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="G148">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2024</v>
+      </c>
+      <c r="H148" s="2">
+        <v>11368</v>
+      </c>
+      <c r="I148">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B149">
-        <v>0.94</v>
+        <v>0.97</v>
       </c>
       <c r="C149" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D149">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="E149" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F149" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="G149">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+      <c r="H149" s="2">
+        <v>10451</v>
+      </c>
+      <c r="I149">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>18</v>
       </c>
@@ -4158,8 +5070,14 @@
       <c r="G150">
         <v>2023</v>
       </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H150" s="2">
+        <v>10451</v>
+      </c>
+      <c r="I150">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>18</v>
       </c>
@@ -4181,703 +5099,2630 @@
       <c r="G151">
         <v>2023</v>
       </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H151" s="2">
+        <v>10451</v>
+      </c>
+      <c r="I151">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="B152">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="C152" t="s">
         <v>24</v>
       </c>
       <c r="D152">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E152" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F152" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="G152">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2024</v>
+      </c>
+      <c r="H152" s="2">
+        <v>11368</v>
+      </c>
+      <c r="I152">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="B153">
-        <v>1.03</v>
+        <v>0.97</v>
       </c>
       <c r="C153" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D153">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E153" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F153" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="G153">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H153" s="2">
+        <v>10451</v>
+      </c>
+      <c r="I153">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B154">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="C154" t="s">
         <v>24</v>
       </c>
       <c r="D154">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="E154" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F154" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G154">
         <v>2023</v>
       </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H154" s="2">
+        <v>94621</v>
+      </c>
+      <c r="I154">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B155">
-        <v>0.94</v>
+        <v>1.04</v>
       </c>
       <c r="C155" t="s">
         <v>25</v>
       </c>
       <c r="D155">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="E155" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F155" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G155">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2024</v>
+      </c>
+      <c r="H155" s="2">
+        <v>94621</v>
+      </c>
+      <c r="I155">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="B156">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="C156" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D156">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E156" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="F156" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="G156">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H156" s="2">
+        <v>95691</v>
+      </c>
+      <c r="I156">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="B157">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="C157" t="s">
         <v>25</v>
       </c>
       <c r="D157">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E157" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="F157" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="G157">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+      <c r="H157" s="2">
+        <v>95691</v>
+      </c>
+      <c r="I157">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="B158">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="C158" t="s">
         <v>24</v>
       </c>
       <c r="D158">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E158" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F158" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G158">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+      <c r="H158" s="2">
+        <v>95691</v>
+      </c>
+      <c r="I158">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="B159">
+        <v>1.07</v>
+      </c>
+      <c r="C159" t="s">
+        <v>24</v>
+      </c>
+      <c r="D159">
+        <v>147</v>
+      </c>
+      <c r="E159" t="s">
+        <v>37</v>
+      </c>
+      <c r="F159" t="s">
+        <v>68</v>
+      </c>
+      <c r="G159">
+        <v>2024</v>
+      </c>
+      <c r="H159" s="2">
+        <v>94621</v>
+      </c>
+      <c r="I159">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B160">
+        <v>1.07</v>
+      </c>
+      <c r="C160" t="s">
+        <v>24</v>
+      </c>
+      <c r="D160">
+        <v>147</v>
+      </c>
+      <c r="E160" t="s">
+        <v>37</v>
+      </c>
+      <c r="F160" t="s">
+        <v>68</v>
+      </c>
+      <c r="G160">
+        <v>2026</v>
+      </c>
+      <c r="H160" s="2">
+        <v>95691</v>
+      </c>
+      <c r="I160">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B161">
         <v>1.04</v>
       </c>
-      <c r="C159" t="s">
-        <v>25</v>
-      </c>
-      <c r="D159">
-        <v>143</v>
-      </c>
-      <c r="E159" t="s">
-        <v>42</v>
-      </c>
-      <c r="F159" t="s">
-        <v>72</v>
-      </c>
-      <c r="G159">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A160" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B160">
-        <v>0.95</v>
-      </c>
-      <c r="C160" t="s">
-        <v>24</v>
-      </c>
-      <c r="D160">
-        <v>134</v>
-      </c>
-      <c r="E160" t="s">
-        <v>61</v>
-      </c>
-      <c r="F160" t="s">
-        <v>89</v>
-      </c>
-      <c r="G160">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A161" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B161">
-        <v>0.91</v>
-      </c>
       <c r="C161" t="s">
         <v>25</v>
       </c>
       <c r="D161">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="E161" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="F161" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="G161">
         <v>2023</v>
       </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H161" s="2">
+        <v>94621</v>
+      </c>
+      <c r="I161">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B162">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="C162" t="s">
         <v>24</v>
       </c>
       <c r="D162">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E162" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F162" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G162">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H162" s="2">
+        <v>19148</v>
+      </c>
+      <c r="I162">
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B163">
-        <v>0.99</v>
+        <v>1.08</v>
       </c>
       <c r="C163" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D163">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E163" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F163" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G163">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+      <c r="H163" s="2">
+        <v>19148</v>
+      </c>
+      <c r="I163">
+        <v>1.1399999999999999</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B164">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="C164" t="s">
         <v>24</v>
       </c>
       <c r="D164">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E164" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="F164" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="G164">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2024</v>
+      </c>
+      <c r="H164" s="2">
+        <v>19148</v>
+      </c>
+      <c r="I164">
+        <v>1.1299999999999999</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B165">
-        <v>0.99</v>
+        <v>1.08</v>
       </c>
       <c r="C165" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D165">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E165" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="F165" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="G165">
         <v>2023</v>
       </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H165" s="2">
+        <v>19148</v>
+      </c>
+      <c r="I165">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B166">
-        <v>0.95</v>
+        <v>1.04</v>
       </c>
       <c r="C166" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D166">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="E166" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F166" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G166">
         <v>2023</v>
       </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H166" s="2">
+        <v>19148</v>
+      </c>
+      <c r="I166">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B167">
+        <v>1.04</v>
+      </c>
+      <c r="C167" t="s">
+        <v>25</v>
+      </c>
+      <c r="D167">
+        <v>143</v>
+      </c>
+      <c r="E167" t="s">
+        <v>42</v>
+      </c>
+      <c r="F167" t="s">
+        <v>72</v>
+      </c>
+      <c r="G167">
+        <v>2024</v>
+      </c>
+      <c r="H167" s="2">
+        <v>19148</v>
+      </c>
+      <c r="I167">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A168" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B168">
+        <v>1.04</v>
+      </c>
+      <c r="C168" t="s">
+        <v>25</v>
+      </c>
+      <c r="D168">
+        <v>143</v>
+      </c>
+      <c r="E168" t="s">
+        <v>42</v>
+      </c>
+      <c r="F168" t="s">
+        <v>72</v>
+      </c>
+      <c r="G168">
+        <v>2025</v>
+      </c>
+      <c r="H168" s="2">
+        <v>19148</v>
+      </c>
+      <c r="I168">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A169" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B169">
+        <v>1.04</v>
+      </c>
+      <c r="C169" t="s">
+        <v>25</v>
+      </c>
+      <c r="D169">
+        <v>143</v>
+      </c>
+      <c r="E169" t="s">
+        <v>42</v>
+      </c>
+      <c r="F169" t="s">
+        <v>72</v>
+      </c>
+      <c r="G169">
+        <v>2026</v>
+      </c>
+      <c r="H169" s="2">
+        <v>19148</v>
+      </c>
+      <c r="I169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A170" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B170">
+        <v>0.95</v>
+      </c>
+      <c r="C170" t="s">
+        <v>24</v>
+      </c>
+      <c r="D170">
+        <v>134</v>
+      </c>
+      <c r="E170" t="s">
+        <v>61</v>
+      </c>
+      <c r="F170" t="s">
+        <v>89</v>
+      </c>
+      <c r="G170">
+        <v>2024</v>
+      </c>
+      <c r="H170" s="2">
+        <v>15212</v>
+      </c>
+      <c r="I170">
         <v>1.01</v>
       </c>
-      <c r="C167" t="s">
-        <v>25</v>
-      </c>
-      <c r="D167">
-        <v>111</v>
-      </c>
-      <c r="E167" t="s">
-        <v>46</v>
-      </c>
-      <c r="F167" t="s">
-        <v>76</v>
-      </c>
-      <c r="G167">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A168" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B168">
-        <v>1.17</v>
-      </c>
-      <c r="C168" t="s">
-        <v>24</v>
-      </c>
-      <c r="D168">
-        <v>113</v>
-      </c>
-      <c r="E168" t="s">
-        <v>35</v>
-      </c>
-      <c r="F168" t="s">
-        <v>66</v>
-      </c>
-      <c r="G168">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A169" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B169">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="C169" t="s">
-        <v>25</v>
-      </c>
-      <c r="D169">
-        <v>113</v>
-      </c>
-      <c r="E169" t="s">
-        <v>35</v>
-      </c>
-      <c r="F169" t="s">
-        <v>66</v>
-      </c>
-      <c r="G169">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A170" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B170">
-        <v>1.05</v>
-      </c>
-      <c r="C170" t="s">
-        <v>24</v>
-      </c>
-      <c r="D170">
-        <v>115</v>
-      </c>
-      <c r="E170" t="s">
-        <v>38</v>
-      </c>
-      <c r="F170" t="s">
-        <v>69</v>
-      </c>
-      <c r="G170">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B171">
-        <v>1.08</v>
+        <v>0.95</v>
       </c>
       <c r="C171" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D171">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="E171" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="F171" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="G171">
         <v>2023</v>
       </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H171" s="2">
+        <v>15212</v>
+      </c>
+      <c r="I171">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B172">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="C172" t="s">
         <v>24</v>
       </c>
       <c r="D172">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="E172" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F172" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G172">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H172" s="2">
+        <v>15212</v>
+      </c>
+      <c r="I172">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B173">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="C173" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D173">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="E173" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F173" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G173">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+      <c r="H173" s="2">
+        <v>15212</v>
+      </c>
+      <c r="I173">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B174">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="C174" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D174">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="E174" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F174" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G174">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2024</v>
+      </c>
+      <c r="H174" s="2">
+        <v>15212</v>
+      </c>
+      <c r="I174">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B175">
-        <v>0.98</v>
+        <v>0.91</v>
       </c>
       <c r="C175" t="s">
         <v>25</v>
       </c>
       <c r="D175">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="E175" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F175" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G175">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2026</v>
+      </c>
+      <c r="H175" s="2">
+        <v>15212</v>
+      </c>
+      <c r="I175">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B176">
-        <v>1.02</v>
+        <v>0.91</v>
       </c>
       <c r="C176" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D176">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E176" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="F176" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G176">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+      <c r="H176" s="2">
+        <v>15212</v>
+      </c>
+      <c r="I176">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B177">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="C177" t="s">
         <v>25</v>
       </c>
       <c r="D177">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E177" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="F177" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G177">
         <v>2023</v>
       </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H177" s="2">
+        <v>15212</v>
+      </c>
+      <c r="I177">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B178">
+        <v>1</v>
+      </c>
+      <c r="C178" t="s">
+        <v>25</v>
+      </c>
+      <c r="D178">
+        <v>135</v>
+      </c>
+      <c r="E178" t="s">
+        <v>51</v>
+      </c>
+      <c r="F178" t="s">
+        <v>80</v>
+      </c>
+      <c r="G178">
+        <v>2026</v>
+      </c>
+      <c r="H178" s="2">
+        <v>92101</v>
+      </c>
+      <c r="I178">
         <v>1.08</v>
       </c>
-      <c r="C178" t="s">
-        <v>24</v>
-      </c>
-      <c r="D178">
-        <v>145</v>
-      </c>
-      <c r="E178" t="s">
-        <v>39</v>
-      </c>
-      <c r="F178" t="s">
-        <v>70</v>
-      </c>
-      <c r="G178">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B179">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="C179" t="s">
         <v>25</v>
       </c>
       <c r="D179">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="E179" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F179" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G179">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+      <c r="H179" s="2">
+        <v>92101</v>
+      </c>
+      <c r="I179">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="B180">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="C180" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D180">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="E180" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="F180" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="G180">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2024</v>
+      </c>
+      <c r="H180" s="2">
+        <v>92101</v>
+      </c>
+      <c r="I180">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="B181">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="C181" t="s">
         <v>25</v>
       </c>
       <c r="D181">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="E181" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="F181" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="G181">
         <v>2023</v>
       </c>
+      <c r="H181" s="2">
+        <v>92101</v>
+      </c>
+      <c r="I181">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A182" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B182">
+        <v>1.01</v>
+      </c>
+      <c r="C182" t="s">
+        <v>24</v>
+      </c>
+      <c r="D182">
+        <v>135</v>
+      </c>
+      <c r="E182" t="s">
+        <v>51</v>
+      </c>
+      <c r="F182" t="s">
+        <v>80</v>
+      </c>
+      <c r="G182">
+        <v>2026</v>
+      </c>
+      <c r="H182" s="2">
+        <v>92101</v>
+      </c>
+      <c r="I182">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A183" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B183">
+        <v>1.01</v>
+      </c>
+      <c r="C183" t="s">
+        <v>24</v>
+      </c>
+      <c r="D183">
+        <v>135</v>
+      </c>
+      <c r="E183" t="s">
+        <v>51</v>
+      </c>
+      <c r="F183" t="s">
+        <v>80</v>
+      </c>
+      <c r="G183">
+        <v>2024</v>
+      </c>
+      <c r="H183" s="2">
+        <v>92101</v>
+      </c>
+      <c r="I183">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A184" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B184">
+        <v>1.01</v>
+      </c>
+      <c r="C184" t="s">
+        <v>24</v>
+      </c>
+      <c r="D184">
+        <v>135</v>
+      </c>
+      <c r="E184" t="s">
+        <v>51</v>
+      </c>
+      <c r="F184" t="s">
+        <v>80</v>
+      </c>
+      <c r="G184">
+        <v>2025</v>
+      </c>
+      <c r="H184" s="2">
+        <v>92101</v>
+      </c>
+      <c r="I184">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A185" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B185">
+        <v>1.01</v>
+      </c>
+      <c r="C185" t="s">
+        <v>24</v>
+      </c>
+      <c r="D185">
+        <v>135</v>
+      </c>
+      <c r="E185" t="s">
+        <v>51</v>
+      </c>
+      <c r="F185" t="s">
+        <v>80</v>
+      </c>
+      <c r="G185">
+        <v>2023</v>
+      </c>
+      <c r="H185" s="2">
+        <v>92101</v>
+      </c>
+      <c r="I185">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A186" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B186">
+        <v>0.98</v>
+      </c>
+      <c r="C186" t="s">
+        <v>25</v>
+      </c>
+      <c r="D186">
+        <v>136</v>
+      </c>
+      <c r="E186" t="s">
+        <v>56</v>
+      </c>
+      <c r="F186" t="s">
+        <v>84</v>
+      </c>
+      <c r="G186">
+        <v>2024</v>
+      </c>
+      <c r="H186" s="2">
+        <v>94107</v>
+      </c>
+      <c r="I186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A187" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B187">
+        <v>0.98</v>
+      </c>
+      <c r="C187" t="s">
+        <v>25</v>
+      </c>
+      <c r="D187">
+        <v>136</v>
+      </c>
+      <c r="E187" t="s">
+        <v>56</v>
+      </c>
+      <c r="F187" t="s">
+        <v>84</v>
+      </c>
+      <c r="G187">
+        <v>2023</v>
+      </c>
+      <c r="H187" s="2">
+        <v>94107</v>
+      </c>
+      <c r="I187">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A188" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B188">
+        <v>0.98</v>
+      </c>
+      <c r="C188" t="s">
+        <v>25</v>
+      </c>
+      <c r="D188">
+        <v>136</v>
+      </c>
+      <c r="E188" t="s">
+        <v>56</v>
+      </c>
+      <c r="F188" t="s">
+        <v>84</v>
+      </c>
+      <c r="G188">
+        <v>2026</v>
+      </c>
+      <c r="H188" s="2">
+        <v>94107</v>
+      </c>
+      <c r="I188">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A189" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B189">
+        <v>0.93</v>
+      </c>
+      <c r="C189" t="s">
+        <v>24</v>
+      </c>
+      <c r="D189">
+        <v>136</v>
+      </c>
+      <c r="E189" t="s">
+        <v>56</v>
+      </c>
+      <c r="F189" t="s">
+        <v>84</v>
+      </c>
+      <c r="G189">
+        <v>2025</v>
+      </c>
+      <c r="H189" s="2">
+        <v>94107</v>
+      </c>
+      <c r="I189">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A190" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B190">
+        <v>0.93</v>
+      </c>
+      <c r="C190" t="s">
+        <v>24</v>
+      </c>
+      <c r="D190">
+        <v>136</v>
+      </c>
+      <c r="E190" t="s">
+        <v>56</v>
+      </c>
+      <c r="F190" t="s">
+        <v>84</v>
+      </c>
+      <c r="G190">
+        <v>2023</v>
+      </c>
+      <c r="H190" s="2">
+        <v>94107</v>
+      </c>
+      <c r="I190">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A191" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B191">
+        <v>0.93</v>
+      </c>
+      <c r="C191" t="s">
+        <v>24</v>
+      </c>
+      <c r="D191">
+        <v>136</v>
+      </c>
+      <c r="E191" t="s">
+        <v>56</v>
+      </c>
+      <c r="F191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G191">
+        <v>2026</v>
+      </c>
+      <c r="H191" s="2">
+        <v>94107</v>
+      </c>
+      <c r="I191">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A192" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B192">
+        <v>0.98</v>
+      </c>
+      <c r="C192" t="s">
+        <v>25</v>
+      </c>
+      <c r="D192">
+        <v>136</v>
+      </c>
+      <c r="E192" t="s">
+        <v>56</v>
+      </c>
+      <c r="F192" t="s">
+        <v>84</v>
+      </c>
+      <c r="G192">
+        <v>2025</v>
+      </c>
+      <c r="H192" s="2">
+        <v>94107</v>
+      </c>
+      <c r="I192">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A193" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B193">
+        <v>0.93</v>
+      </c>
+      <c r="C193" t="s">
+        <v>24</v>
+      </c>
+      <c r="D193">
+        <v>136</v>
+      </c>
+      <c r="E193" t="s">
+        <v>56</v>
+      </c>
+      <c r="F193" t="s">
+        <v>84</v>
+      </c>
+      <c r="G193">
+        <v>2024</v>
+      </c>
+      <c r="H193" s="2">
+        <v>94107</v>
+      </c>
+      <c r="I193">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A194" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B194">
+        <v>0.9</v>
+      </c>
+      <c r="C194" t="s">
+        <v>25</v>
+      </c>
+      <c r="D194">
+        <v>137</v>
+      </c>
+      <c r="E194" t="s">
+        <v>64</v>
+      </c>
+      <c r="F194" t="s">
+        <v>92</v>
+      </c>
+      <c r="G194">
+        <v>2025</v>
+      </c>
+      <c r="H194" s="2">
+        <v>98134</v>
+      </c>
+      <c r="I194">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A195" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B195">
+        <v>0.91</v>
+      </c>
+      <c r="C195" t="s">
+        <v>24</v>
+      </c>
+      <c r="D195">
+        <v>137</v>
+      </c>
+      <c r="E195" t="s">
+        <v>64</v>
+      </c>
+      <c r="F195" t="s">
+        <v>92</v>
+      </c>
+      <c r="G195">
+        <v>2023</v>
+      </c>
+      <c r="H195" s="2">
+        <v>98134</v>
+      </c>
+      <c r="I195">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A196" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B196">
+        <v>0.9</v>
+      </c>
+      <c r="C196" t="s">
+        <v>25</v>
+      </c>
+      <c r="D196">
+        <v>137</v>
+      </c>
+      <c r="E196" t="s">
+        <v>64</v>
+      </c>
+      <c r="F196" t="s">
+        <v>92</v>
+      </c>
+      <c r="G196">
+        <v>2023</v>
+      </c>
+      <c r="H196" s="2">
+        <v>98134</v>
+      </c>
+      <c r="I196">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A197" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B197">
+        <v>0.9</v>
+      </c>
+      <c r="C197" t="s">
+        <v>25</v>
+      </c>
+      <c r="D197">
+        <v>137</v>
+      </c>
+      <c r="E197" t="s">
+        <v>64</v>
+      </c>
+      <c r="F197" t="s">
+        <v>92</v>
+      </c>
+      <c r="G197">
+        <v>2024</v>
+      </c>
+      <c r="H197" s="2">
+        <v>98134</v>
+      </c>
+      <c r="I197">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A198" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B198">
+        <v>0.9</v>
+      </c>
+      <c r="C198" t="s">
+        <v>25</v>
+      </c>
+      <c r="D198">
+        <v>137</v>
+      </c>
+      <c r="E198" t="s">
+        <v>64</v>
+      </c>
+      <c r="F198" t="s">
+        <v>92</v>
+      </c>
+      <c r="G198">
+        <v>2026</v>
+      </c>
+      <c r="H198" s="2">
+        <v>98134</v>
+      </c>
+      <c r="I198">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A199" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B199">
+        <v>0.91</v>
+      </c>
+      <c r="C199" t="s">
+        <v>24</v>
+      </c>
+      <c r="D199">
+        <v>137</v>
+      </c>
+      <c r="E199" t="s">
+        <v>64</v>
+      </c>
+      <c r="F199" t="s">
+        <v>92</v>
+      </c>
+      <c r="G199">
+        <v>2025</v>
+      </c>
+      <c r="H199" s="2">
+        <v>98134</v>
+      </c>
+      <c r="I199">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A200" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B200">
+        <v>0.91</v>
+      </c>
+      <c r="C200" t="s">
+        <v>24</v>
+      </c>
+      <c r="D200">
+        <v>137</v>
+      </c>
+      <c r="E200" t="s">
+        <v>64</v>
+      </c>
+      <c r="F200" t="s">
+        <v>92</v>
+      </c>
+      <c r="G200">
+        <v>2024</v>
+      </c>
+      <c r="H200" s="2">
+        <v>98134</v>
+      </c>
+      <c r="I200">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A201" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B201">
+        <v>0.91</v>
+      </c>
+      <c r="C201" t="s">
+        <v>24</v>
+      </c>
+      <c r="D201">
+        <v>137</v>
+      </c>
+      <c r="E201" t="s">
+        <v>64</v>
+      </c>
+      <c r="F201" t="s">
+        <v>92</v>
+      </c>
+      <c r="G201">
+        <v>2026</v>
+      </c>
+      <c r="H201" s="2">
+        <v>98134</v>
+      </c>
+      <c r="I201">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A202" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B202">
+        <v>0.94</v>
+      </c>
+      <c r="C202" t="s">
+        <v>25</v>
+      </c>
+      <c r="D202">
+        <v>138</v>
+      </c>
+      <c r="E202" t="s">
+        <v>62</v>
+      </c>
+      <c r="F202" t="s">
+        <v>90</v>
+      </c>
+      <c r="G202">
+        <v>2024</v>
+      </c>
+      <c r="H202" s="2">
+        <v>63102</v>
+      </c>
+      <c r="I202">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A203" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B203">
+        <v>0.94</v>
+      </c>
+      <c r="C203" t="s">
+        <v>25</v>
+      </c>
+      <c r="D203">
+        <v>138</v>
+      </c>
+      <c r="E203" t="s">
+        <v>62</v>
+      </c>
+      <c r="F203" t="s">
+        <v>90</v>
+      </c>
+      <c r="G203">
+        <v>2023</v>
+      </c>
+      <c r="H203" s="2">
+        <v>63102</v>
+      </c>
+      <c r="I203">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A204" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B204">
+        <v>0.94</v>
+      </c>
+      <c r="C204" t="s">
+        <v>24</v>
+      </c>
+      <c r="D204">
+        <v>138</v>
+      </c>
+      <c r="E204" t="s">
+        <v>62</v>
+      </c>
+      <c r="F204" t="s">
+        <v>90</v>
+      </c>
+      <c r="G204">
+        <v>2025</v>
+      </c>
+      <c r="H204" s="2">
+        <v>63102</v>
+      </c>
+      <c r="I204">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A205" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B205">
+        <v>0.94</v>
+      </c>
+      <c r="C205" t="s">
+        <v>24</v>
+      </c>
+      <c r="D205">
+        <v>138</v>
+      </c>
+      <c r="E205" t="s">
+        <v>62</v>
+      </c>
+      <c r="F205" t="s">
+        <v>90</v>
+      </c>
+      <c r="G205">
+        <v>2024</v>
+      </c>
+      <c r="H205" s="2">
+        <v>63102</v>
+      </c>
+      <c r="I205">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A206" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B206">
+        <v>0.94</v>
+      </c>
+      <c r="C206" t="s">
+        <v>25</v>
+      </c>
+      <c r="D206">
+        <v>138</v>
+      </c>
+      <c r="E206" t="s">
+        <v>62</v>
+      </c>
+      <c r="F206" t="s">
+        <v>90</v>
+      </c>
+      <c r="G206">
+        <v>2025</v>
+      </c>
+      <c r="H206" s="2">
+        <v>63102</v>
+      </c>
+      <c r="I206">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A207" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B207">
+        <v>0.94</v>
+      </c>
+      <c r="C207" t="s">
+        <v>24</v>
+      </c>
+      <c r="D207">
+        <v>138</v>
+      </c>
+      <c r="E207" t="s">
+        <v>62</v>
+      </c>
+      <c r="F207" t="s">
+        <v>90</v>
+      </c>
+      <c r="G207">
+        <v>2023</v>
+      </c>
+      <c r="H207" s="2">
+        <v>63102</v>
+      </c>
+      <c r="I207">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A208" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B208">
+        <v>0.94</v>
+      </c>
+      <c r="C208" t="s">
+        <v>24</v>
+      </c>
+      <c r="D208">
+        <v>138</v>
+      </c>
+      <c r="E208" t="s">
+        <v>62</v>
+      </c>
+      <c r="F208" t="s">
+        <v>90</v>
+      </c>
+      <c r="G208">
+        <v>2026</v>
+      </c>
+      <c r="H208" s="2">
+        <v>63102</v>
+      </c>
+      <c r="I208">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B209">
+        <v>0.94</v>
+      </c>
+      <c r="C209" t="s">
+        <v>25</v>
+      </c>
+      <c r="D209">
+        <v>138</v>
+      </c>
+      <c r="E209" t="s">
+        <v>62</v>
+      </c>
+      <c r="F209" t="s">
+        <v>90</v>
+      </c>
+      <c r="G209">
+        <v>2026</v>
+      </c>
+      <c r="H209" s="2">
+        <v>63102</v>
+      </c>
+      <c r="I209">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A210" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B210">
+        <v>1.08</v>
+      </c>
+      <c r="C210" t="s">
+        <v>25</v>
+      </c>
+      <c r="D210">
+        <v>139</v>
+      </c>
+      <c r="E210" t="s">
+        <v>57</v>
+      </c>
+      <c r="F210" t="s">
+        <v>85</v>
+      </c>
+      <c r="G210">
+        <v>2025</v>
+      </c>
+      <c r="H210" s="2">
+        <v>33614</v>
+      </c>
+      <c r="I210">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B211">
+        <v>1.08</v>
+      </c>
+      <c r="C211" t="s">
+        <v>25</v>
+      </c>
+      <c r="D211">
+        <v>139</v>
+      </c>
+      <c r="E211" t="s">
+        <v>57</v>
+      </c>
+      <c r="F211" t="s">
+        <v>85</v>
+      </c>
+      <c r="G211">
+        <v>2026</v>
+      </c>
+      <c r="H211" s="2">
+        <v>33614</v>
+      </c>
+      <c r="I211">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B212">
+        <v>0.99</v>
+      </c>
+      <c r="C212" t="s">
+        <v>25</v>
+      </c>
+      <c r="D212">
+        <v>139</v>
+      </c>
+      <c r="E212" t="s">
+        <v>57</v>
+      </c>
+      <c r="F212" t="s">
+        <v>85</v>
+      </c>
+      <c r="G212">
+        <v>2024</v>
+      </c>
+      <c r="H212" s="2">
+        <v>33705</v>
+      </c>
+      <c r="I212">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B213">
+        <v>0.99</v>
+      </c>
+      <c r="C213" t="s">
+        <v>25</v>
+      </c>
+      <c r="D213">
+        <v>139</v>
+      </c>
+      <c r="E213" t="s">
+        <v>57</v>
+      </c>
+      <c r="F213" t="s">
+        <v>85</v>
+      </c>
+      <c r="G213">
+        <v>2023</v>
+      </c>
+      <c r="H213" s="2">
+        <v>33705</v>
+      </c>
+      <c r="I213">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A214" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B214">
+        <v>1</v>
+      </c>
+      <c r="C214" t="s">
+        <v>24</v>
+      </c>
+      <c r="D214">
+        <v>139</v>
+      </c>
+      <c r="E214" t="s">
+        <v>57</v>
+      </c>
+      <c r="F214" t="s">
+        <v>85</v>
+      </c>
+      <c r="G214">
+        <v>2025</v>
+      </c>
+      <c r="H214" s="2">
+        <v>33614</v>
+      </c>
+      <c r="I214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B215">
+        <v>0.92</v>
+      </c>
+      <c r="C215" t="s">
+        <v>24</v>
+      </c>
+      <c r="D215">
+        <v>139</v>
+      </c>
+      <c r="E215" t="s">
+        <v>57</v>
+      </c>
+      <c r="F215" t="s">
+        <v>85</v>
+      </c>
+      <c r="G215">
+        <v>2024</v>
+      </c>
+      <c r="H215" s="2">
+        <v>33705</v>
+      </c>
+      <c r="I215">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B216">
+        <v>0.92</v>
+      </c>
+      <c r="C216" t="s">
+        <v>24</v>
+      </c>
+      <c r="D216">
+        <v>139</v>
+      </c>
+      <c r="E216" t="s">
+        <v>57</v>
+      </c>
+      <c r="F216" t="s">
+        <v>85</v>
+      </c>
+      <c r="G216">
+        <v>2023</v>
+      </c>
+      <c r="H216" s="2">
+        <v>33705</v>
+      </c>
+      <c r="I216">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B217">
+        <v>1</v>
+      </c>
+      <c r="C217" t="s">
+        <v>24</v>
+      </c>
+      <c r="D217">
+        <v>139</v>
+      </c>
+      <c r="E217" t="s">
+        <v>57</v>
+      </c>
+      <c r="F217" t="s">
+        <v>85</v>
+      </c>
+      <c r="G217">
+        <v>2026</v>
+      </c>
+      <c r="H217" s="2">
+        <v>33614</v>
+      </c>
+      <c r="I217">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B218">
+        <v>0.99</v>
+      </c>
+      <c r="C218" t="s">
+        <v>25</v>
+      </c>
+      <c r="D218">
+        <v>140</v>
+      </c>
+      <c r="E218" t="s">
+        <v>41</v>
+      </c>
+      <c r="F218" t="s">
+        <v>71</v>
+      </c>
+      <c r="G218">
+        <v>2024</v>
+      </c>
+      <c r="H218" s="2">
+        <v>76011</v>
+      </c>
+      <c r="I218">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B219">
+        <v>0.99</v>
+      </c>
+      <c r="C219" t="s">
+        <v>25</v>
+      </c>
+      <c r="D219">
+        <v>140</v>
+      </c>
+      <c r="E219" t="s">
+        <v>41</v>
+      </c>
+      <c r="F219" t="s">
+        <v>71</v>
+      </c>
+      <c r="G219">
+        <v>2023</v>
+      </c>
+      <c r="H219" s="2">
+        <v>76011</v>
+      </c>
+      <c r="I219">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B220">
+        <v>1.05</v>
+      </c>
+      <c r="C220" t="s">
+        <v>24</v>
+      </c>
+      <c r="D220">
+        <v>140</v>
+      </c>
+      <c r="E220" t="s">
+        <v>41</v>
+      </c>
+      <c r="F220" t="s">
+        <v>71</v>
+      </c>
+      <c r="G220">
+        <v>2024</v>
+      </c>
+      <c r="H220" s="2">
+        <v>76011</v>
+      </c>
+      <c r="I220">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B221">
+        <v>1.05</v>
+      </c>
+      <c r="C221" t="s">
+        <v>24</v>
+      </c>
+      <c r="D221">
+        <v>140</v>
+      </c>
+      <c r="E221" t="s">
+        <v>41</v>
+      </c>
+      <c r="F221" t="s">
+        <v>71</v>
+      </c>
+      <c r="G221">
+        <v>2023</v>
+      </c>
+      <c r="H221" s="2">
+        <v>76011</v>
+      </c>
+      <c r="I221">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A222" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B222">
+        <v>0.99</v>
+      </c>
+      <c r="C222" t="s">
+        <v>25</v>
+      </c>
+      <c r="D222">
+        <v>140</v>
+      </c>
+      <c r="E222" t="s">
+        <v>41</v>
+      </c>
+      <c r="F222" t="s">
+        <v>71</v>
+      </c>
+      <c r="G222">
+        <v>2025</v>
+      </c>
+      <c r="H222" s="2">
+        <v>76011</v>
+      </c>
+      <c r="I222">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B223">
+        <v>1.05</v>
+      </c>
+      <c r="C223" t="s">
+        <v>24</v>
+      </c>
+      <c r="D223">
+        <v>140</v>
+      </c>
+      <c r="E223" t="s">
+        <v>41</v>
+      </c>
+      <c r="F223" t="s">
+        <v>71</v>
+      </c>
+      <c r="G223">
+        <v>2025</v>
+      </c>
+      <c r="H223" s="2">
+        <v>76011</v>
+      </c>
+      <c r="I223">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B224">
+        <v>1.05</v>
+      </c>
+      <c r="C224" t="s">
+        <v>24</v>
+      </c>
+      <c r="D224">
+        <v>140</v>
+      </c>
+      <c r="E224" t="s">
+        <v>41</v>
+      </c>
+      <c r="F224" t="s">
+        <v>71</v>
+      </c>
+      <c r="G224">
+        <v>2026</v>
+      </c>
+      <c r="H224" s="2">
+        <v>76011</v>
+      </c>
+      <c r="I224">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B225">
+        <v>0.99</v>
+      </c>
+      <c r="C225" t="s">
+        <v>25</v>
+      </c>
+      <c r="D225">
+        <v>140</v>
+      </c>
+      <c r="E225" t="s">
+        <v>41</v>
+      </c>
+      <c r="F225" t="s">
+        <v>71</v>
+      </c>
+      <c r="G225">
+        <v>2026</v>
+      </c>
+      <c r="H225" s="2">
+        <v>76011</v>
+      </c>
+      <c r="I225">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A226" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B226">
+        <v>1.05</v>
+      </c>
+      <c r="C226" t="s">
+        <v>25</v>
+      </c>
+      <c r="D226">
+        <v>141</v>
+      </c>
+      <c r="E226" t="s">
+        <v>47</v>
+      </c>
+      <c r="F226" t="s">
+        <v>77</v>
+      </c>
+      <c r="G226">
+        <v>2026</v>
+      </c>
+      <c r="H226" s="2">
+        <v>0</v>
+      </c>
+      <c r="I226">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A227" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B227">
+        <v>1.05</v>
+      </c>
+      <c r="C227" t="s">
+        <v>25</v>
+      </c>
+      <c r="D227">
+        <v>141</v>
+      </c>
+      <c r="E227" t="s">
+        <v>47</v>
+      </c>
+      <c r="F227" t="s">
+        <v>77</v>
+      </c>
+      <c r="G227">
+        <v>2023</v>
+      </c>
+      <c r="H227" s="2">
+        <v>0</v>
+      </c>
+      <c r="I227">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A228" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B228">
+        <v>0.97</v>
+      </c>
+      <c r="C228" t="s">
+        <v>24</v>
+      </c>
+      <c r="D228">
+        <v>141</v>
+      </c>
+      <c r="E228" t="s">
+        <v>47</v>
+      </c>
+      <c r="F228" t="s">
+        <v>77</v>
+      </c>
+      <c r="G228">
+        <v>2026</v>
+      </c>
+      <c r="H228" s="2">
+        <v>0</v>
+      </c>
+      <c r="I228">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A229" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B229">
+        <v>1.05</v>
+      </c>
+      <c r="C229" t="s">
+        <v>25</v>
+      </c>
+      <c r="D229">
+        <v>141</v>
+      </c>
+      <c r="E229" t="s">
+        <v>47</v>
+      </c>
+      <c r="F229" t="s">
+        <v>77</v>
+      </c>
+      <c r="G229">
+        <v>2024</v>
+      </c>
+      <c r="H229" s="2">
+        <v>0</v>
+      </c>
+      <c r="I229">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A230" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B230">
+        <v>1.05</v>
+      </c>
+      <c r="C230" t="s">
+        <v>25</v>
+      </c>
+      <c r="D230">
+        <v>141</v>
+      </c>
+      <c r="E230" t="s">
+        <v>47</v>
+      </c>
+      <c r="F230" t="s">
+        <v>77</v>
+      </c>
+      <c r="G230">
+        <v>2025</v>
+      </c>
+      <c r="H230" s="2">
+        <v>0</v>
+      </c>
+      <c r="I230">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A231" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B231">
+        <v>0.97</v>
+      </c>
+      <c r="C231" t="s">
+        <v>24</v>
+      </c>
+      <c r="D231">
+        <v>141</v>
+      </c>
+      <c r="E231" t="s">
+        <v>47</v>
+      </c>
+      <c r="F231" t="s">
+        <v>77</v>
+      </c>
+      <c r="G231">
+        <v>2025</v>
+      </c>
+      <c r="H231" s="2">
+        <v>0</v>
+      </c>
+      <c r="I231">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B232">
+        <v>0.97</v>
+      </c>
+      <c r="C232" t="s">
+        <v>24</v>
+      </c>
+      <c r="D232">
+        <v>141</v>
+      </c>
+      <c r="E232" t="s">
+        <v>47</v>
+      </c>
+      <c r="F232" t="s">
+        <v>77</v>
+      </c>
+      <c r="G232">
+        <v>2024</v>
+      </c>
+      <c r="H232" s="2">
+        <v>0</v>
+      </c>
+      <c r="I232">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A233" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B233">
+        <v>0.97</v>
+      </c>
+      <c r="C233" t="s">
+        <v>24</v>
+      </c>
+      <c r="D233">
+        <v>141</v>
+      </c>
+      <c r="E233" t="s">
+        <v>47</v>
+      </c>
+      <c r="F233" t="s">
+        <v>77</v>
+      </c>
+      <c r="G233">
+        <v>2023</v>
+      </c>
+      <c r="H233" s="2">
+        <v>0</v>
+      </c>
+      <c r="I233">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A234" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B234">
+        <v>0.99</v>
+      </c>
+      <c r="C234" t="s">
+        <v>24</v>
+      </c>
+      <c r="D234">
+        <v>120</v>
+      </c>
+      <c r="E234" t="s">
+        <v>49</v>
+      </c>
+      <c r="F234" t="s">
+        <v>79</v>
+      </c>
+      <c r="G234">
+        <v>2023</v>
+      </c>
+      <c r="H234" s="2">
+        <v>20003</v>
+      </c>
+      <c r="I234">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B235">
+        <v>1.03</v>
+      </c>
+      <c r="C235" t="s">
+        <v>25</v>
+      </c>
+      <c r="D235">
+        <v>120</v>
+      </c>
+      <c r="E235" t="s">
+        <v>49</v>
+      </c>
+      <c r="F235" t="s">
+        <v>79</v>
+      </c>
+      <c r="G235">
+        <v>2023</v>
+      </c>
+      <c r="H235" s="2">
+        <v>20003</v>
+      </c>
+      <c r="I235">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A236" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B236">
+        <v>1.03</v>
+      </c>
+      <c r="C236" t="s">
+        <v>25</v>
+      </c>
+      <c r="D236">
+        <v>120</v>
+      </c>
+      <c r="E236" t="s">
+        <v>49</v>
+      </c>
+      <c r="F236" t="s">
+        <v>79</v>
+      </c>
+      <c r="G236">
+        <v>2024</v>
+      </c>
+      <c r="H236" s="2">
+        <v>20003</v>
+      </c>
+      <c r="I236">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A237" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B237">
+        <v>0.99</v>
+      </c>
+      <c r="C237" t="s">
+        <v>24</v>
+      </c>
+      <c r="D237">
+        <v>120</v>
+      </c>
+      <c r="E237" t="s">
+        <v>49</v>
+      </c>
+      <c r="F237" t="s">
+        <v>79</v>
+      </c>
+      <c r="G237">
+        <v>2026</v>
+      </c>
+      <c r="H237" s="2">
+        <v>20003</v>
+      </c>
+      <c r="I237">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A238" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B238">
+        <v>0.99</v>
+      </c>
+      <c r="C238" t="s">
+        <v>24</v>
+      </c>
+      <c r="D238">
+        <v>120</v>
+      </c>
+      <c r="E238" t="s">
+        <v>49</v>
+      </c>
+      <c r="F238" t="s">
+        <v>79</v>
+      </c>
+      <c r="G238">
+        <v>2024</v>
+      </c>
+      <c r="H238" s="2">
+        <v>20003</v>
+      </c>
+      <c r="I238">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A239" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B239">
+        <v>0.99</v>
+      </c>
+      <c r="C239" t="s">
+        <v>24</v>
+      </c>
+      <c r="D239">
+        <v>120</v>
+      </c>
+      <c r="E239" t="s">
+        <v>49</v>
+      </c>
+      <c r="F239" t="s">
+        <v>79</v>
+      </c>
+      <c r="G239">
+        <v>2025</v>
+      </c>
+      <c r="H239" s="2">
+        <v>20003</v>
+      </c>
+      <c r="I239">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A240" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B240">
+        <v>1.03</v>
+      </c>
+      <c r="C240" t="s">
+        <v>25</v>
+      </c>
+      <c r="D240">
+        <v>120</v>
+      </c>
+      <c r="E240" t="s">
+        <v>49</v>
+      </c>
+      <c r="F240" t="s">
+        <v>79</v>
+      </c>
+      <c r="G240">
+        <v>2026</v>
+      </c>
+      <c r="H240" s="2">
+        <v>20003</v>
+      </c>
+      <c r="I240">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A241" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B241">
+        <v>1.03</v>
+      </c>
+      <c r="C241" t="s">
+        <v>25</v>
+      </c>
+      <c r="D241">
+        <v>120</v>
+      </c>
+      <c r="E241" t="s">
+        <v>49</v>
+      </c>
+      <c r="F241" t="s">
+        <v>79</v>
+      </c>
+      <c r="G241">
+        <v>2025</v>
+      </c>
+      <c r="H241" s="2">
+        <v>20003</v>
+      </c>
+      <c r="I241">
+        <v>0.96</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G61" xr:uid="{B19E0F6F-4091-44B6-8908-ADD872FB2D48}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G61">
-      <sortCondition ref="E1:E61"/>
+  <autoFilter ref="A1:I241" xr:uid="{B19E0F6F-4091-44B6-8908-ADD872FB2D48}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I241">
+      <sortCondition ref="A1:A241"/>
     </sortState>
   </autoFilter>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>